--- a/upload/66666.xlsx
+++ b/upload/66666.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d33043be37511ad6/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A83A504-62A8-4ACB-A003-C5E44CC15E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{9A83A504-62A8-4ACB-A003-C5E44CC15E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B65122C-3A57-4211-8A59-92538BC66CFC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{412CD3B9-14C6-4315-B0CD-98BB2622AFF8}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$B$2:$H$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$B$2:$H$303</definedName>
     <definedName name="AccountCodes">'[1]دليل الحسابات'!$A$6:$A$203</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="110">
   <si>
     <t>تاريخ القيد</t>
   </si>
@@ -408,6 +408,12 @@
   </si>
   <si>
     <t>مورد 3 شركة اشبيجيال</t>
+  </si>
+  <si>
+    <t>فاتورة كهرباء 2</t>
+  </si>
+  <si>
+    <t>مخزون البضاعة</t>
   </si>
 </sst>
 </file>
@@ -417,7 +423,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,6 +469,20 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -543,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -572,17 +592,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -605,7 +638,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4F6F8"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -619,7 +652,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFF4F6F8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1102,6 +1135,813 @@
             <v>قائمة الدخل</v>
           </cell>
         </row>
+        <row r="31">
+          <cell r="A31"/>
+          <cell r="B31"/>
+          <cell r="C31"/>
+          <cell r="D31"/>
+          <cell r="E31"/>
+        </row>
+        <row r="32">
+          <cell r="A32"/>
+          <cell r="B32"/>
+          <cell r="C32"/>
+          <cell r="D32"/>
+          <cell r="E32"/>
+        </row>
+        <row r="33">
+          <cell r="A33"/>
+          <cell r="B33"/>
+          <cell r="C33"/>
+          <cell r="D33"/>
+          <cell r="E33"/>
+        </row>
+        <row r="34">
+          <cell r="A34"/>
+          <cell r="B34"/>
+          <cell r="C34"/>
+          <cell r="D34"/>
+          <cell r="E34"/>
+        </row>
+        <row r="35">
+          <cell r="A35"/>
+          <cell r="B35"/>
+          <cell r="C35"/>
+          <cell r="D35"/>
+          <cell r="E35"/>
+        </row>
+        <row r="36">
+          <cell r="A36"/>
+          <cell r="B36"/>
+          <cell r="C36"/>
+          <cell r="D36"/>
+          <cell r="E36"/>
+        </row>
+        <row r="37">
+          <cell r="A37"/>
+          <cell r="B37"/>
+          <cell r="C37"/>
+          <cell r="D37"/>
+          <cell r="E37"/>
+        </row>
+        <row r="38">
+          <cell r="A38"/>
+          <cell r="B38"/>
+          <cell r="C38"/>
+          <cell r="D38"/>
+          <cell r="E38"/>
+        </row>
+        <row r="39">
+          <cell r="A39"/>
+          <cell r="B39"/>
+          <cell r="C39"/>
+          <cell r="D39"/>
+          <cell r="E39"/>
+        </row>
+        <row r="40">
+          <cell r="A40"/>
+          <cell r="B40"/>
+          <cell r="C40"/>
+          <cell r="D40"/>
+          <cell r="E40"/>
+        </row>
+        <row r="41">
+          <cell r="A41"/>
+          <cell r="B41"/>
+          <cell r="C41"/>
+          <cell r="D41"/>
+          <cell r="E41"/>
+        </row>
+        <row r="42">
+          <cell r="A42"/>
+          <cell r="B42"/>
+          <cell r="C42"/>
+          <cell r="D42"/>
+          <cell r="E42"/>
+        </row>
+        <row r="43">
+          <cell r="A43"/>
+          <cell r="B43"/>
+          <cell r="C43"/>
+          <cell r="D43"/>
+          <cell r="E43"/>
+        </row>
+        <row r="44">
+          <cell r="A44"/>
+          <cell r="B44"/>
+          <cell r="C44"/>
+          <cell r="D44"/>
+          <cell r="E44"/>
+        </row>
+        <row r="45">
+          <cell r="A45"/>
+          <cell r="B45"/>
+          <cell r="C45"/>
+          <cell r="D45"/>
+          <cell r="E45"/>
+        </row>
+        <row r="46">
+          <cell r="A46"/>
+          <cell r="B46"/>
+          <cell r="C46"/>
+          <cell r="D46"/>
+          <cell r="E46"/>
+        </row>
+        <row r="47">
+          <cell r="A47"/>
+          <cell r="B47"/>
+          <cell r="C47"/>
+          <cell r="D47"/>
+          <cell r="E47"/>
+        </row>
+        <row r="48">
+          <cell r="A48"/>
+          <cell r="B48"/>
+          <cell r="C48"/>
+          <cell r="D48"/>
+          <cell r="E48"/>
+        </row>
+        <row r="49">
+          <cell r="A49"/>
+          <cell r="B49"/>
+          <cell r="C49"/>
+          <cell r="D49"/>
+          <cell r="E49"/>
+        </row>
+        <row r="50">
+          <cell r="A50"/>
+          <cell r="B50"/>
+          <cell r="C50"/>
+          <cell r="D50"/>
+          <cell r="E50"/>
+        </row>
+        <row r="51">
+          <cell r="A51"/>
+          <cell r="B51"/>
+          <cell r="C51"/>
+          <cell r="D51"/>
+          <cell r="E51"/>
+        </row>
+        <row r="52">
+          <cell r="A52"/>
+          <cell r="B52"/>
+          <cell r="C52"/>
+          <cell r="D52"/>
+          <cell r="E52"/>
+        </row>
+        <row r="53">
+          <cell r="A53"/>
+          <cell r="B53"/>
+          <cell r="C53"/>
+          <cell r="D53"/>
+          <cell r="E53"/>
+        </row>
+        <row r="54">
+          <cell r="A54"/>
+          <cell r="B54"/>
+          <cell r="C54"/>
+          <cell r="D54"/>
+          <cell r="E54"/>
+        </row>
+        <row r="55">
+          <cell r="A55"/>
+          <cell r="B55"/>
+          <cell r="C55"/>
+          <cell r="D55"/>
+          <cell r="E55"/>
+        </row>
+        <row r="56">
+          <cell r="A56"/>
+          <cell r="B56"/>
+          <cell r="C56"/>
+          <cell r="D56"/>
+          <cell r="E56"/>
+        </row>
+        <row r="57">
+          <cell r="A57"/>
+          <cell r="B57"/>
+          <cell r="C57"/>
+          <cell r="D57"/>
+          <cell r="E57"/>
+        </row>
+        <row r="58">
+          <cell r="A58"/>
+          <cell r="B58"/>
+          <cell r="C58"/>
+          <cell r="D58"/>
+          <cell r="E58"/>
+        </row>
+        <row r="59">
+          <cell r="A59"/>
+          <cell r="B59"/>
+          <cell r="C59"/>
+          <cell r="D59"/>
+          <cell r="E59"/>
+        </row>
+        <row r="60">
+          <cell r="A60"/>
+          <cell r="B60"/>
+          <cell r="C60"/>
+          <cell r="D60"/>
+          <cell r="E60"/>
+        </row>
+        <row r="61">
+          <cell r="A61"/>
+          <cell r="B61"/>
+          <cell r="C61"/>
+          <cell r="D61"/>
+          <cell r="E61"/>
+        </row>
+        <row r="62">
+          <cell r="A62"/>
+          <cell r="B62"/>
+          <cell r="C62"/>
+          <cell r="D62"/>
+          <cell r="E62"/>
+        </row>
+        <row r="63">
+          <cell r="A63"/>
+          <cell r="B63"/>
+          <cell r="C63"/>
+          <cell r="D63"/>
+          <cell r="E63"/>
+        </row>
+        <row r="64">
+          <cell r="A64"/>
+          <cell r="B64"/>
+          <cell r="C64"/>
+          <cell r="D64"/>
+          <cell r="E64"/>
+        </row>
+        <row r="65">
+          <cell r="A65"/>
+          <cell r="B65"/>
+          <cell r="C65"/>
+          <cell r="D65"/>
+          <cell r="E65"/>
+        </row>
+        <row r="66">
+          <cell r="A66"/>
+          <cell r="B66"/>
+          <cell r="C66"/>
+          <cell r="D66"/>
+          <cell r="E66"/>
+        </row>
+        <row r="67">
+          <cell r="A67"/>
+          <cell r="B67"/>
+          <cell r="C67"/>
+          <cell r="D67"/>
+          <cell r="E67"/>
+        </row>
+        <row r="68">
+          <cell r="A68"/>
+          <cell r="B68"/>
+          <cell r="C68"/>
+          <cell r="D68"/>
+          <cell r="E68"/>
+        </row>
+        <row r="69">
+          <cell r="A69"/>
+          <cell r="B69"/>
+          <cell r="C69"/>
+          <cell r="D69"/>
+          <cell r="E69"/>
+        </row>
+        <row r="70">
+          <cell r="A70"/>
+          <cell r="B70"/>
+          <cell r="C70"/>
+          <cell r="D70"/>
+          <cell r="E70"/>
+        </row>
+        <row r="71">
+          <cell r="A71"/>
+          <cell r="B71"/>
+          <cell r="C71"/>
+          <cell r="D71"/>
+          <cell r="E71"/>
+        </row>
+        <row r="72">
+          <cell r="A72"/>
+          <cell r="B72"/>
+          <cell r="C72"/>
+          <cell r="D72"/>
+          <cell r="E72"/>
+        </row>
+        <row r="73">
+          <cell r="A73"/>
+          <cell r="B73"/>
+          <cell r="C73"/>
+          <cell r="D73"/>
+          <cell r="E73"/>
+        </row>
+        <row r="74">
+          <cell r="A74"/>
+          <cell r="B74"/>
+          <cell r="C74"/>
+          <cell r="D74"/>
+          <cell r="E74"/>
+        </row>
+        <row r="75">
+          <cell r="A75"/>
+          <cell r="B75"/>
+          <cell r="C75"/>
+          <cell r="D75"/>
+          <cell r="E75"/>
+        </row>
+        <row r="76">
+          <cell r="A76"/>
+          <cell r="B76"/>
+          <cell r="C76"/>
+          <cell r="D76"/>
+          <cell r="E76"/>
+        </row>
+        <row r="77">
+          <cell r="A77"/>
+          <cell r="B77"/>
+          <cell r="C77"/>
+          <cell r="D77"/>
+          <cell r="E77"/>
+        </row>
+        <row r="78">
+          <cell r="A78"/>
+          <cell r="B78"/>
+          <cell r="C78"/>
+          <cell r="D78"/>
+          <cell r="E78"/>
+        </row>
+        <row r="79">
+          <cell r="A79"/>
+          <cell r="B79"/>
+          <cell r="C79"/>
+          <cell r="D79"/>
+          <cell r="E79"/>
+        </row>
+        <row r="80">
+          <cell r="A80"/>
+          <cell r="B80"/>
+          <cell r="C80"/>
+          <cell r="D80"/>
+          <cell r="E80"/>
+        </row>
+        <row r="81">
+          <cell r="A81"/>
+          <cell r="B81"/>
+          <cell r="C81"/>
+          <cell r="D81"/>
+          <cell r="E81"/>
+        </row>
+        <row r="82">
+          <cell r="A82"/>
+          <cell r="B82"/>
+          <cell r="C82"/>
+          <cell r="D82"/>
+          <cell r="E82"/>
+        </row>
+        <row r="83">
+          <cell r="A83"/>
+          <cell r="B83"/>
+          <cell r="C83"/>
+          <cell r="D83"/>
+          <cell r="E83"/>
+        </row>
+        <row r="84">
+          <cell r="A84"/>
+          <cell r="B84"/>
+          <cell r="C84"/>
+          <cell r="D84"/>
+          <cell r="E84"/>
+        </row>
+        <row r="85">
+          <cell r="A85"/>
+          <cell r="B85"/>
+          <cell r="C85"/>
+          <cell r="D85"/>
+          <cell r="E85"/>
+        </row>
+        <row r="86">
+          <cell r="A86"/>
+          <cell r="B86"/>
+          <cell r="C86"/>
+          <cell r="D86"/>
+          <cell r="E86"/>
+        </row>
+        <row r="87">
+          <cell r="A87"/>
+          <cell r="B87"/>
+          <cell r="C87"/>
+          <cell r="D87"/>
+          <cell r="E87"/>
+        </row>
+        <row r="88">
+          <cell r="A88"/>
+          <cell r="B88"/>
+          <cell r="C88"/>
+          <cell r="D88"/>
+          <cell r="E88"/>
+        </row>
+        <row r="89">
+          <cell r="A89"/>
+          <cell r="B89"/>
+          <cell r="C89"/>
+          <cell r="D89"/>
+          <cell r="E89"/>
+        </row>
+        <row r="90">
+          <cell r="A90"/>
+          <cell r="B90"/>
+          <cell r="C90"/>
+          <cell r="D90"/>
+          <cell r="E90"/>
+        </row>
+        <row r="91">
+          <cell r="A91"/>
+          <cell r="B91"/>
+          <cell r="C91"/>
+          <cell r="D91"/>
+          <cell r="E91"/>
+        </row>
+        <row r="92">
+          <cell r="A92"/>
+          <cell r="B92"/>
+          <cell r="C92"/>
+          <cell r="D92"/>
+          <cell r="E92"/>
+        </row>
+        <row r="93">
+          <cell r="A93"/>
+          <cell r="B93"/>
+          <cell r="C93"/>
+          <cell r="D93"/>
+          <cell r="E93"/>
+        </row>
+        <row r="94">
+          <cell r="A94"/>
+          <cell r="B94"/>
+          <cell r="C94"/>
+          <cell r="D94"/>
+          <cell r="E94"/>
+        </row>
+        <row r="95">
+          <cell r="A95"/>
+          <cell r="B95"/>
+          <cell r="C95"/>
+          <cell r="D95"/>
+          <cell r="E95"/>
+        </row>
+        <row r="96">
+          <cell r="A96"/>
+          <cell r="B96"/>
+          <cell r="C96"/>
+          <cell r="D96"/>
+          <cell r="E96"/>
+        </row>
+        <row r="97">
+          <cell r="A97"/>
+          <cell r="B97"/>
+          <cell r="C97"/>
+          <cell r="D97"/>
+          <cell r="E97"/>
+        </row>
+        <row r="98">
+          <cell r="A98"/>
+          <cell r="B98"/>
+          <cell r="C98"/>
+          <cell r="D98"/>
+          <cell r="E98"/>
+        </row>
+        <row r="99">
+          <cell r="A99"/>
+          <cell r="B99"/>
+          <cell r="C99"/>
+          <cell r="D99"/>
+          <cell r="E99"/>
+        </row>
+        <row r="100">
+          <cell r="A100"/>
+          <cell r="B100"/>
+          <cell r="C100"/>
+          <cell r="D100"/>
+          <cell r="E100"/>
+        </row>
+        <row r="101">
+          <cell r="A101"/>
+          <cell r="B101"/>
+          <cell r="C101"/>
+          <cell r="D101"/>
+          <cell r="E101"/>
+        </row>
+        <row r="102">
+          <cell r="A102"/>
+          <cell r="B102"/>
+          <cell r="C102"/>
+          <cell r="D102"/>
+          <cell r="E102"/>
+        </row>
+        <row r="103">
+          <cell r="A103"/>
+        </row>
+        <row r="104">
+          <cell r="A104"/>
+        </row>
+        <row r="105">
+          <cell r="A105"/>
+        </row>
+        <row r="106">
+          <cell r="A106"/>
+        </row>
+        <row r="107">
+          <cell r="A107"/>
+        </row>
+        <row r="108">
+          <cell r="A108"/>
+        </row>
+        <row r="109">
+          <cell r="A109"/>
+        </row>
+        <row r="110">
+          <cell r="A110"/>
+        </row>
+        <row r="111">
+          <cell r="A111"/>
+        </row>
+        <row r="112">
+          <cell r="A112"/>
+        </row>
+        <row r="113">
+          <cell r="A113"/>
+        </row>
+        <row r="114">
+          <cell r="A114"/>
+        </row>
+        <row r="115">
+          <cell r="A115"/>
+        </row>
+        <row r="116">
+          <cell r="A116"/>
+        </row>
+        <row r="117">
+          <cell r="A117"/>
+        </row>
+        <row r="118">
+          <cell r="A118"/>
+        </row>
+        <row r="119">
+          <cell r="A119"/>
+        </row>
+        <row r="120">
+          <cell r="A120"/>
+        </row>
+        <row r="121">
+          <cell r="A121"/>
+        </row>
+        <row r="122">
+          <cell r="A122"/>
+        </row>
+        <row r="123">
+          <cell r="A123"/>
+        </row>
+        <row r="124">
+          <cell r="A124"/>
+        </row>
+        <row r="125">
+          <cell r="A125"/>
+        </row>
+        <row r="126">
+          <cell r="A126"/>
+        </row>
+        <row r="127">
+          <cell r="A127"/>
+        </row>
+        <row r="128">
+          <cell r="A128"/>
+        </row>
+        <row r="129">
+          <cell r="A129"/>
+        </row>
+        <row r="130">
+          <cell r="A130"/>
+        </row>
+        <row r="131">
+          <cell r="A131"/>
+        </row>
+        <row r="132">
+          <cell r="A132"/>
+        </row>
+        <row r="133">
+          <cell r="A133"/>
+        </row>
+        <row r="134">
+          <cell r="A134"/>
+        </row>
+        <row r="135">
+          <cell r="A135"/>
+        </row>
+        <row r="136">
+          <cell r="A136"/>
+        </row>
+        <row r="137">
+          <cell r="A137"/>
+        </row>
+        <row r="138">
+          <cell r="A138"/>
+        </row>
+        <row r="139">
+          <cell r="A139"/>
+        </row>
+        <row r="140">
+          <cell r="A140"/>
+        </row>
+        <row r="141">
+          <cell r="A141"/>
+        </row>
+        <row r="142">
+          <cell r="A142"/>
+        </row>
+        <row r="143">
+          <cell r="A143"/>
+        </row>
+        <row r="144">
+          <cell r="A144"/>
+        </row>
+        <row r="145">
+          <cell r="A145"/>
+        </row>
+        <row r="146">
+          <cell r="A146"/>
+        </row>
+        <row r="147">
+          <cell r="A147"/>
+        </row>
+        <row r="148">
+          <cell r="A148"/>
+        </row>
+        <row r="149">
+          <cell r="A149"/>
+        </row>
+        <row r="150">
+          <cell r="A150"/>
+        </row>
+        <row r="151">
+          <cell r="A151"/>
+        </row>
+        <row r="152">
+          <cell r="A152"/>
+        </row>
+        <row r="153">
+          <cell r="A153"/>
+        </row>
+        <row r="154">
+          <cell r="A154"/>
+        </row>
+        <row r="155">
+          <cell r="A155"/>
+        </row>
+        <row r="156">
+          <cell r="A156"/>
+        </row>
+        <row r="157">
+          <cell r="A157"/>
+        </row>
+        <row r="158">
+          <cell r="A158"/>
+        </row>
+        <row r="159">
+          <cell r="A159"/>
+        </row>
+        <row r="160">
+          <cell r="A160"/>
+        </row>
+        <row r="161">
+          <cell r="A161"/>
+        </row>
+        <row r="162">
+          <cell r="A162"/>
+        </row>
+        <row r="163">
+          <cell r="A163"/>
+        </row>
+        <row r="164">
+          <cell r="A164"/>
+        </row>
+        <row r="165">
+          <cell r="A165"/>
+        </row>
+        <row r="166">
+          <cell r="A166"/>
+        </row>
+        <row r="167">
+          <cell r="A167"/>
+        </row>
+        <row r="168">
+          <cell r="A168"/>
+        </row>
+        <row r="169">
+          <cell r="A169"/>
+        </row>
+        <row r="170">
+          <cell r="A170"/>
+        </row>
+        <row r="171">
+          <cell r="A171"/>
+        </row>
+        <row r="172">
+          <cell r="A172"/>
+        </row>
+        <row r="173">
+          <cell r="A173"/>
+        </row>
+        <row r="174">
+          <cell r="A174"/>
+        </row>
+        <row r="175">
+          <cell r="A175"/>
+        </row>
+        <row r="176">
+          <cell r="A176"/>
+        </row>
+        <row r="177">
+          <cell r="A177"/>
+        </row>
+        <row r="178">
+          <cell r="A178"/>
+        </row>
+        <row r="179">
+          <cell r="A179"/>
+        </row>
+        <row r="180">
+          <cell r="A180"/>
+        </row>
+        <row r="181">
+          <cell r="A181"/>
+        </row>
+        <row r="182">
+          <cell r="A182"/>
+        </row>
+        <row r="183">
+          <cell r="A183"/>
+        </row>
+        <row r="184">
+          <cell r="A184"/>
+        </row>
+        <row r="185">
+          <cell r="A185"/>
+        </row>
+        <row r="186">
+          <cell r="A186"/>
+        </row>
+        <row r="187">
+          <cell r="A187"/>
+        </row>
+        <row r="188">
+          <cell r="A188"/>
+        </row>
+        <row r="189">
+          <cell r="A189"/>
+        </row>
+        <row r="190">
+          <cell r="A190"/>
+        </row>
+        <row r="191">
+          <cell r="A191"/>
+        </row>
+        <row r="192">
+          <cell r="A192"/>
+        </row>
+        <row r="193">
+          <cell r="A193"/>
+        </row>
+        <row r="194">
+          <cell r="A194"/>
+        </row>
+        <row r="195">
+          <cell r="A195"/>
+        </row>
+        <row r="196">
+          <cell r="A196"/>
+        </row>
+        <row r="197">
+          <cell r="A197"/>
+        </row>
+        <row r="198">
+          <cell r="A198"/>
+        </row>
+        <row r="199">
+          <cell r="A199"/>
+        </row>
+        <row r="200">
+          <cell r="A200"/>
+        </row>
+        <row r="201">
+          <cell r="A201"/>
+        </row>
+        <row r="202">
+          <cell r="A202"/>
+        </row>
+        <row r="203">
+          <cell r="A203"/>
+        </row>
       </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -1115,6 +1955,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1434,11 +2278,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A10BBC1-C1E5-406F-ACCB-ABF92E7F8642}">
-  <dimension ref="B1:H302"/>
+  <dimension ref="B1:H303"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="13.19921875" customWidth="1"/>
-    <col min="4" max="4" width="12.8984375" customWidth="1"/>
+    <col min="4" max="4" width="12.8984375" style="14" customWidth="1"/>
     <col min="5" max="5" width="18.3984375" customWidth="1"/>
     <col min="8" max="8" width="43.796875" customWidth="1"/>
   </cols>
@@ -1475,10 +2319,10 @@
       <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="15">
         <v>5015</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F3" s="8">
@@ -1496,10 +2340,10 @@
       <c r="C4" s="6">
         <v>1</v>
       </c>
-      <c r="D4" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="8"/>
@@ -1517,10 +2361,10 @@
       <c r="C5" s="6">
         <v>2</v>
       </c>
-      <c r="D5" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F5" s="8">
@@ -1538,10 +2382,10 @@
       <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="15">
         <v>3001</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>96</v>
       </c>
       <c r="F6" s="8"/>
@@ -1559,10 +2403,10 @@
       <c r="C7" s="6">
         <v>2.5</v>
       </c>
-      <c r="D7" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="D7" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F7" s="8">
@@ -1580,10 +2424,10 @@
       <c r="C8" s="6">
         <v>3</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="15">
         <v>3001</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>96</v>
       </c>
       <c r="F8" s="8"/>
@@ -1601,10 +2445,10 @@
       <c r="C9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="15">
         <v>5015</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F9" s="8">
@@ -1622,10 +2466,10 @@
       <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F10" s="8"/>
@@ -1643,10 +2487,10 @@
       <c r="C11" s="6">
         <v>4.5535714285714297</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="15">
         <v>5015</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F11" s="8">
@@ -1664,10 +2508,10 @@
       <c r="C12" s="6">
         <v>5.0238095238095299</v>
       </c>
-      <c r="D12" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F12" s="8"/>
@@ -1685,10 +2529,10 @@
       <c r="C13" s="6">
         <v>6</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="15">
         <v>5015</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8">
@@ -1706,10 +2550,10 @@
       <c r="C14" s="6">
         <v>6</v>
       </c>
-      <c r="D14" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="D14" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F14" s="8"/>
@@ -1727,10 +2571,10 @@
       <c r="C15" s="6">
         <v>6.7232142857142803</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="15">
         <v>5015</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8">
@@ -1748,10 +2592,10 @@
       <c r="C16" s="6">
         <v>7.2547619047619003</v>
       </c>
-      <c r="D16" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="D16" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F16" s="8"/>
@@ -1769,10 +2613,10 @@
       <c r="C17" s="6">
         <v>7.7863095238095203</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="15">
         <v>5015</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F17" s="8">
@@ -1790,10 +2634,10 @@
       <c r="C18" s="6">
         <v>8.3178571428571395</v>
       </c>
-      <c r="D18" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F18" s="8"/>
@@ -1811,10 +2655,10 @@
       <c r="C19" s="6">
         <v>8.8494047619047507</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="15">
         <v>5015</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F19" s="8">
@@ -1832,10 +2676,10 @@
       <c r="C20" s="6">
         <v>9.3809523809523707</v>
       </c>
-      <c r="D20" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F20" s="8"/>
@@ -1853,10 +2697,10 @@
       <c r="C21" s="6">
         <v>9.9124999999999908</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="15">
         <v>5015</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F21" s="8">
@@ -1874,10 +2718,10 @@
       <c r="C22" s="6">
         <v>10.4440476190476</v>
       </c>
-      <c r="D22" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="D22" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F22" s="8"/>
@@ -1895,10 +2739,10 @@
       <c r="C23" s="6">
         <v>10.975595238095201</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="15">
         <v>5015</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F23" s="8">
@@ -1916,10 +2760,10 @@
       <c r="C24" s="6">
         <v>11.507142857142799</v>
       </c>
-      <c r="D24" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E24" s="14" t="s">
+      <c r="D24" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="8"/>
@@ -1937,10 +2781,10 @@
       <c r="C25" s="6">
         <v>12.038690476190499</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="16">
         <v>5022</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F25" s="8">
@@ -1958,10 +2802,10 @@
       <c r="C26" s="6">
         <v>12.5702380952381</v>
       </c>
-      <c r="D26" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E26" s="14" t="s">
+      <c r="D26" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F26" s="8"/>
@@ -1979,10 +2823,10 @@
       <c r="C27" s="6">
         <v>13.1017857142857</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="15">
         <v>5015</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F27" s="8">
@@ -2000,17 +2844,19 @@
       <c r="C28" s="6">
         <v>13.633333333333301</v>
       </c>
-      <c r="D28" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="D28" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8">
         <v>4300</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" spans="2:8" ht="17.399999999999999">
       <c r="B29" s="5">
@@ -2019,10 +2865,10 @@
       <c r="C29" s="6">
         <v>14.1648809523809</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="15">
         <v>5015</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F29" s="8">
@@ -2040,17 +2886,19 @@
       <c r="C30" s="6">
         <v>14.6964285714285</v>
       </c>
-      <c r="D30" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E30" s="14" t="s">
+      <c r="D30" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8">
         <v>300</v>
       </c>
-      <c r="H30" s="9"/>
+      <c r="H30" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="31" spans="2:8" ht="17.399999999999999">
       <c r="B31" s="5">
@@ -2059,10 +2907,10 @@
       <c r="C31" s="6">
         <v>15.2279761904762</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="15">
         <v>5015</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F31" s="8">
@@ -2080,17 +2928,19 @@
       <c r="C32" s="6">
         <v>15.759523809523801</v>
       </c>
-      <c r="D32" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E32" s="14" t="s">
+      <c r="D32" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
         <v>1000</v>
       </c>
-      <c r="H32" s="9"/>
+      <c r="H32" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" spans="2:8" ht="18" thickBot="1">
       <c r="B33" s="5">
@@ -2099,10 +2949,10 @@
       <c r="C33" s="6">
         <v>16.291071428571399</v>
       </c>
-      <c r="D33" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E33" s="14" t="s">
+      <c r="D33" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F33" s="8">
@@ -2120,10 +2970,10 @@
       <c r="C34" s="6">
         <v>16.822619047619</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="15">
         <v>3001</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="10" t="s">
         <v>96</v>
       </c>
       <c r="F34" s="8"/>
@@ -2141,10 +2991,10 @@
       <c r="C35" s="6">
         <v>17.3541666666666</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="15">
         <v>5015</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F35" s="8">
@@ -2162,17 +3012,19 @@
       <c r="C36" s="6">
         <v>17.8857142857143</v>
       </c>
-      <c r="D36" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E36" s="14" t="s">
+      <c r="D36" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8">
         <v>350</v>
       </c>
-      <c r="H36" s="9"/>
+      <c r="H36" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="37" spans="2:8" ht="17.399999999999999">
       <c r="B37" s="5">
@@ -2181,10 +3033,10 @@
       <c r="C37" s="6">
         <v>18.417261904761901</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="15">
         <v>5015</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F37" s="8">
@@ -2202,17 +3054,19 @@
       <c r="C38" s="6">
         <v>18.948809523809501</v>
       </c>
-      <c r="D38" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E38" s="14" t="s">
+      <c r="D38" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8">
         <v>2000</v>
       </c>
-      <c r="H38" s="9"/>
+      <c r="H38" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="39" spans="2:8" ht="18" thickBot="1">
       <c r="B39" s="5">
@@ -2221,10 +3075,10 @@
       <c r="C39" s="6">
         <v>19.480357142857098</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="16">
         <v>5002</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F39" s="8">
@@ -2242,17 +3096,19 @@
       <c r="C40" s="6">
         <v>20.011904761904699</v>
       </c>
-      <c r="D40" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E40" s="14" t="s">
+      <c r="D40" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8">
         <v>2000</v>
       </c>
-      <c r="H40" s="9"/>
+      <c r="H40" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="41" spans="2:8" ht="18" thickBot="1">
       <c r="B41" s="5">
@@ -2261,10 +3117,10 @@
       <c r="C41" s="6">
         <v>20.543452380952299</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="16">
         <v>5002</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F41" s="8">
@@ -2282,17 +3138,19 @@
       <c r="C42" s="6">
         <v>21.074999999999999</v>
       </c>
-      <c r="D42" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E42" s="14" t="s">
+      <c r="D42" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8">
         <v>1500</v>
       </c>
-      <c r="H42" s="9"/>
+      <c r="H42" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="43" spans="2:8" ht="17.399999999999999">
       <c r="B43" s="5">
@@ -2301,10 +3159,10 @@
       <c r="C43" s="6">
         <v>21.6065476190476</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="15">
         <v>5003</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="10" t="s">
         <v>99</v>
       </c>
       <c r="F43" s="8">
@@ -2322,17 +3180,19 @@
       <c r="C44" s="6">
         <v>22.1380952380952</v>
       </c>
-      <c r="D44" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E44" s="14" t="s">
+      <c r="D44" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8">
         <v>2000</v>
       </c>
-      <c r="H44" s="9"/>
+      <c r="H44" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="45" spans="2:8" ht="17.399999999999999">
       <c r="B45" s="5">
@@ -2341,10 +3201,10 @@
       <c r="C45" s="6">
         <v>22.669642857142801</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="15">
         <v>5015</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F45" s="8">
@@ -2362,17 +3222,19 @@
       <c r="C46" s="6">
         <v>23.201190476190401</v>
       </c>
-      <c r="D46" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E46" s="14" t="s">
+      <c r="D46" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E46" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8">
         <v>430</v>
       </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="47" spans="2:8" ht="17.399999999999999">
       <c r="B47" s="5">
@@ -2381,10 +3243,10 @@
       <c r="C47" s="6">
         <v>23.732738095238101</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="15">
         <v>3001</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="10" t="s">
         <v>96</v>
       </c>
       <c r="F47" s="8">
@@ -2402,17 +3264,19 @@
       <c r="C48" s="6">
         <v>24.264285714285698</v>
       </c>
-      <c r="D48" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E48" s="14" t="s">
+      <c r="D48" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8">
         <v>6915</v>
       </c>
-      <c r="H48" s="9"/>
+      <c r="H48" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="49" spans="2:8" ht="17.399999999999999">
       <c r="B49" s="5">
@@ -2421,10 +3285,10 @@
       <c r="C49" s="6">
         <v>24.795833333333299</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="15">
         <v>5015</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F49" s="8">
@@ -2442,17 +3306,19 @@
       <c r="C50" s="6">
         <v>25.327380952380899</v>
       </c>
-      <c r="D50" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E50" s="14" t="s">
+      <c r="D50" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8">
         <v>500</v>
       </c>
-      <c r="H50" s="9"/>
+      <c r="H50" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="51" spans="2:8" ht="17.399999999999999">
       <c r="B51" s="5">
@@ -2461,10 +3327,10 @@
       <c r="C51" s="6">
         <v>25.8589285714285</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="15">
         <v>5015</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F51" s="8">
@@ -2482,17 +3348,19 @@
       <c r="C52" s="6">
         <v>26.3904761904761</v>
       </c>
-      <c r="D52" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E52" s="14" t="s">
+      <c r="D52" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E52" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
         <v>2000</v>
       </c>
-      <c r="H52" s="9"/>
+      <c r="H52" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="53" spans="2:8" ht="18" thickBot="1">
       <c r="B53" s="5">
@@ -2501,10 +3369,10 @@
       <c r="C53" s="6">
         <v>26.9220238095238</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="16">
         <v>5002</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F53" s="8">
@@ -2522,17 +3390,19 @@
       <c r="C54" s="6">
         <v>27.453571428571401</v>
       </c>
-      <c r="D54" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E54" s="14" t="s">
+      <c r="D54" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
         <v>100</v>
       </c>
-      <c r="H54" s="9"/>
+      <c r="H54" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="55" spans="2:8" ht="18" thickBot="1">
       <c r="B55" s="5">
@@ -2541,10 +3411,10 @@
       <c r="C55" s="6">
         <v>27.985119047619001</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="16">
         <v>5002</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F55" s="8">
@@ -2562,17 +3432,19 @@
       <c r="C56" s="6">
         <v>28.516666666666602</v>
       </c>
-      <c r="D56" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E56" s="14" t="s">
+      <c r="D56" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
         <v>500</v>
       </c>
-      <c r="H56" s="9"/>
+      <c r="H56" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="57" spans="2:8" ht="17.399999999999999">
       <c r="B57" s="5">
@@ -2581,10 +3453,10 @@
       <c r="C57" s="6">
         <v>29.048214285714199</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="15">
         <v>5015</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F57" s="8">
@@ -2602,17 +3474,19 @@
       <c r="C58" s="6">
         <v>29.579761904761799</v>
       </c>
-      <c r="D58" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="D58" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
         <v>6000</v>
       </c>
-      <c r="H58" s="9"/>
+      <c r="H58" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="59" spans="2:8" ht="17.399999999999999">
       <c r="B59" s="5">
@@ -2621,10 +3495,10 @@
       <c r="C59" s="6">
         <v>30.111309523809499</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="15">
         <v>5015</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F59" s="8">
@@ -2642,17 +3516,19 @@
       <c r="C60" s="6">
         <v>30.6428571428571</v>
       </c>
-      <c r="D60" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E60" s="14" t="s">
+      <c r="D60" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8">
         <v>100</v>
       </c>
-      <c r="H60" s="9"/>
+      <c r="H60" s="9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="61" spans="2:8" ht="17.399999999999999">
       <c r="B61" s="5">
@@ -2661,10 +3537,10 @@
       <c r="C61" s="6">
         <v>31.1744047619047</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="15">
         <v>5015</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F61" s="8">
@@ -2682,17 +3558,19 @@
       <c r="C62" s="6">
         <v>31.705952380952301</v>
       </c>
-      <c r="D62" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E62" s="14" t="s">
+      <c r="D62" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8">
         <v>2300</v>
       </c>
-      <c r="H62" s="9"/>
+      <c r="H62" s="9" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="63" spans="2:8" ht="17.399999999999999">
       <c r="B63" s="5">
@@ -2701,10 +3579,10 @@
       <c r="C63" s="6">
         <v>32.237499999999898</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="15">
         <v>5015</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F63" s="8">
@@ -2722,17 +3600,19 @@
       <c r="C64" s="6">
         <v>32.769047619047598</v>
       </c>
-      <c r="D64" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E64" s="14" t="s">
+      <c r="D64" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8">
         <v>200</v>
       </c>
-      <c r="H64" s="9"/>
+      <c r="H64" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="65" spans="2:8" ht="17.399999999999999">
       <c r="B65" s="5">
@@ -2741,10 +3621,10 @@
       <c r="C65" s="6">
         <v>33.300595238095198</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="15">
         <v>5015</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F65" s="8">
@@ -2762,17 +3642,19 @@
       <c r="C66" s="6">
         <v>33.832142857142799</v>
       </c>
-      <c r="D66" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E66" s="14" t="s">
+      <c r="D66" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8">
         <v>570</v>
       </c>
-      <c r="H66" s="9"/>
+      <c r="H66" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="67" spans="2:8" ht="18" thickBot="1">
       <c r="B67" s="5">
@@ -2781,10 +3663,10 @@
       <c r="C67" s="6">
         <v>34.363690476190399</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="16">
         <v>5002</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F67" s="8">
@@ -2802,17 +3684,19 @@
       <c r="C68" s="6">
         <v>34.895238095238</v>
       </c>
-      <c r="D68" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E68" s="14" t="s">
+      <c r="D68" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8">
         <v>400</v>
       </c>
-      <c r="H68" s="9"/>
+      <c r="H68" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="5">
@@ -2821,7 +3705,7 @@
       <c r="C69" s="6">
         <v>35.4267857142856</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="18">
         <v>2211</v>
       </c>
       <c r="E69" s="7" t="s">
@@ -2842,31 +3726,32 @@
       <c r="C70" s="6">
         <v>35.9583333333333</v>
       </c>
-      <c r="D70" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E70" s="14" t="s">
+      <c r="D70" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E70" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8">
         <v>5000</v>
       </c>
-      <c r="H70" s="9"/>
-    </row>
-    <row r="71" spans="2:8">
+      <c r="H70" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="17.399999999999999">
       <c r="B71" s="5">
         <v>46190</v>
       </c>
       <c r="C71" s="6">
         <v>36.489880952380901</v>
       </c>
-      <c r="D71" s="6">
-        <v>5301</v>
-      </c>
-      <c r="E71" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D71,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>مصروفات تقطيع ولزق شريط</v>
+      <c r="D71" s="18">
+        <v>5015</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="F71" s="8">
         <v>1000</v>
@@ -2883,17 +3768,19 @@
       <c r="C72" s="6">
         <v>37.021428571428501</v>
       </c>
-      <c r="D72" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E72" s="14" t="s">
+      <c r="D72" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E72" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8">
         <v>1000</v>
       </c>
-      <c r="H72" s="9"/>
+      <c r="H72" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="73" spans="2:8" ht="18" thickBot="1">
       <c r="B73" s="5">
@@ -2902,10 +3789,10 @@
       <c r="C73" s="6">
         <v>37.552976190476102</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="16">
         <v>5002</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="E73" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F73" s="8">
@@ -2923,17 +3810,19 @@
       <c r="C74" s="6">
         <v>38.084523809523702</v>
       </c>
-      <c r="D74" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E74" s="14" t="s">
+      <c r="D74" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E74" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8">
         <v>2000</v>
       </c>
-      <c r="H74" s="9"/>
+      <c r="H74" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="75" spans="2:8" ht="18" thickBot="1">
       <c r="B75" s="5">
@@ -2942,10 +3831,10 @@
       <c r="C75" s="6">
         <v>38.616071428571402</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="16">
         <v>5002</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="E75" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F75" s="8">
@@ -2963,31 +3852,32 @@
       <c r="C76" s="6">
         <v>39.147619047619003</v>
       </c>
-      <c r="D76" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E76" s="14" t="s">
+      <c r="D76" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E76" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8">
         <v>1000</v>
       </c>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" spans="2:8">
+      <c r="H76" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="17.399999999999999">
       <c r="B77" s="5">
         <v>46194</v>
       </c>
       <c r="C77" s="6">
         <v>39.679166666666603</v>
       </c>
-      <c r="D77" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E77" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D77,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D77" s="18">
+        <v>5015</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="F77" s="8">
         <v>2000</v>
@@ -3004,17 +3894,19 @@
       <c r="C78" s="6">
         <v>40.210714285714197</v>
       </c>
-      <c r="D78" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E78" s="14" t="s">
+      <c r="D78" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8">
         <v>2000</v>
       </c>
-      <c r="H78" s="9"/>
+      <c r="H78" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="79" spans="2:8" ht="18" thickBot="1">
       <c r="B79" s="5">
@@ -3023,10 +3915,10 @@
       <c r="C79" s="6">
         <v>40.742261904761797</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="16">
         <v>5022</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E79" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F79" s="8">
@@ -3044,17 +3936,19 @@
       <c r="C80" s="6">
         <v>41.273809523809398</v>
       </c>
-      <c r="D80" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E80" s="14" t="s">
+      <c r="D80" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8">
         <v>100</v>
       </c>
-      <c r="H80" s="9"/>
+      <c r="H80" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="81" spans="2:8" ht="17.399999999999999">
       <c r="B81" s="5">
@@ -3063,10 +3957,10 @@
       <c r="C81" s="6">
         <v>41.805357142857098</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="15">
         <v>5015</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F81" s="8">
@@ -3084,17 +3978,19 @@
       <c r="C82" s="6">
         <v>42.336904761904698</v>
       </c>
-      <c r="D82" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E82" s="14" t="s">
+      <c r="D82" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E82" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8">
         <v>500</v>
       </c>
-      <c r="H82" s="9"/>
+      <c r="H82" s="9" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="83" spans="2:8" ht="17.399999999999999">
       <c r="B83" s="5">
@@ -3103,10 +3999,10 @@
       <c r="C83" s="6">
         <v>42.868452380952299</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="15">
         <v>5015</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F83" s="8">
@@ -3124,17 +4020,19 @@
       <c r="C84" s="6">
         <v>43.399999999999899</v>
       </c>
-      <c r="D84" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E84" s="14" t="s">
+      <c r="D84" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E84" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8">
         <v>1000</v>
       </c>
-      <c r="H84" s="9"/>
+      <c r="H84" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="85" spans="2:8" ht="17.399999999999999">
       <c r="B85" s="5">
@@ -3143,10 +4041,10 @@
       <c r="C85" s="6">
         <v>43.9315476190475</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="15">
         <v>5015</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F85" s="8">
@@ -3164,17 +4062,19 @@
       <c r="C86" s="6">
         <v>44.4630952380952</v>
       </c>
-      <c r="D86" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E86" s="14" t="s">
+      <c r="D86" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8">
         <v>1605</v>
       </c>
-      <c r="H86" s="9"/>
+      <c r="H86" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="87" spans="2:8" ht="18" thickBot="1">
       <c r="B87" s="5">
@@ -3183,10 +4083,10 @@
       <c r="C87" s="6">
         <v>44.9946428571428</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="16">
         <v>5022</v>
       </c>
-      <c r="E87" s="13" t="s">
+      <c r="E87" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F87" s="8">
@@ -3204,17 +4104,19 @@
       <c r="C88" s="6">
         <v>45.526190476190401</v>
       </c>
-      <c r="D88" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E88" s="14" t="s">
+      <c r="D88" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E88" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8">
         <v>1000</v>
       </c>
-      <c r="H88" s="9"/>
+      <c r="H88" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="89" spans="2:8" ht="18" thickBot="1">
       <c r="B89" s="5">
@@ -3223,10 +4125,10 @@
       <c r="C89" s="6">
         <v>46.057738095238001</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="16">
         <v>5022</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F89" s="8">
@@ -3244,17 +4146,19 @@
       <c r="C90" s="6">
         <v>46.589285714285602</v>
       </c>
-      <c r="D90" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E90" s="14" t="s">
+      <c r="D90" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8">
         <v>730</v>
       </c>
-      <c r="H90" s="9"/>
+      <c r="H90" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="91" spans="2:8" ht="17.399999999999999">
       <c r="B91" s="5">
@@ -3263,10 +4167,10 @@
       <c r="C91" s="6">
         <v>47.120833333333202</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="15">
         <v>5015</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F91" s="8">
@@ -3284,17 +4188,19 @@
       <c r="C92" s="6">
         <v>47.652380952380902</v>
       </c>
-      <c r="D92" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E92" s="14" t="s">
+      <c r="D92" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E92" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8">
         <v>1900</v>
       </c>
-      <c r="H92" s="9"/>
+      <c r="H92" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="93" spans="2:8" ht="18" thickBot="1">
       <c r="B93" s="5">
@@ -3303,10 +4209,10 @@
       <c r="C93" s="6">
         <v>48.183928571428503</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="16">
         <v>5022</v>
       </c>
-      <c r="E93" s="13" t="s">
+      <c r="E93" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F93" s="8">
@@ -3324,17 +4230,19 @@
       <c r="C94" s="6">
         <v>48.715476190476103</v>
       </c>
-      <c r="D94" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E94" s="14" t="s">
+      <c r="D94" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E94" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8">
         <v>200</v>
       </c>
-      <c r="H94" s="9"/>
+      <c r="H94" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="95" spans="2:8">
       <c r="B95" s="5">
@@ -3343,7 +4251,7 @@
       <c r="C95" s="6">
         <v>49.247023809523697</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="17">
         <v>2212</v>
       </c>
       <c r="E95" s="7" t="s">
@@ -3364,17 +4272,19 @@
       <c r="C96" s="6">
         <v>49.778571428571297</v>
       </c>
-      <c r="D96" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E96" s="14" t="s">
+      <c r="D96" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E96" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8">
         <v>2500</v>
       </c>
-      <c r="H96" s="9"/>
+      <c r="H96" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="5">
@@ -3383,7 +4293,7 @@
       <c r="C97" s="6">
         <v>50.310119047618898</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="17">
         <v>2211</v>
       </c>
       <c r="E97" s="7" t="s">
@@ -3404,17 +4314,19 @@
       <c r="C98" s="6">
         <v>50.841666666666598</v>
       </c>
-      <c r="D98" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E98" s="14" t="s">
+      <c r="D98" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E98" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8">
         <v>6000</v>
       </c>
-      <c r="H98" s="9"/>
+      <c r="H98" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="99" spans="2:8" ht="17.399999999999999">
       <c r="B99" s="5">
@@ -3423,10 +4335,10 @@
       <c r="C99" s="6">
         <v>51.373214285714198</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="15">
         <v>5015</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F99" s="8">
@@ -3444,17 +4356,19 @@
       <c r="C100" s="6">
         <v>51.904761904761799</v>
       </c>
-      <c r="D100" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E100" s="14" t="s">
+      <c r="D100" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E100" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8">
         <v>1530</v>
       </c>
-      <c r="H100" s="9"/>
+      <c r="H100" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="101" spans="2:8" ht="18" thickBot="1">
       <c r="B101" s="5">
@@ -3463,10 +4377,10 @@
       <c r="C101" s="6">
         <v>52.436309523809399</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="16">
         <v>5002</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E101" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F101" s="8">
@@ -3484,17 +4398,19 @@
       <c r="C102" s="6">
         <v>52.967857142857</v>
       </c>
-      <c r="D102" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E102" s="14" t="s">
+      <c r="D102" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E102" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8">
         <v>4000</v>
       </c>
-      <c r="H102" s="9"/>
+      <c r="H102" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="103" spans="2:8" ht="18" thickBot="1">
       <c r="B103" s="5">
@@ -3503,10 +4419,10 @@
       <c r="C103" s="6">
         <v>53.4994047619047</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="16">
         <v>5002</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E103" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F103" s="8">
@@ -3524,17 +4440,19 @@
       <c r="C104" s="6">
         <v>54.0309523809523</v>
       </c>
-      <c r="D104" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E104" s="14" t="s">
+      <c r="D104" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E104" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F104" s="8"/>
       <c r="G104" s="8">
         <v>800</v>
       </c>
-      <c r="H104" s="9"/>
+      <c r="H104" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="105" spans="2:8">
       <c r="B105" s="5">
@@ -3543,12 +4461,11 @@
       <c r="C105" s="6">
         <v>54.562499999999901</v>
       </c>
-      <c r="D105" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E105" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D105,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D105" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F105" s="8">
         <v>3600</v>
@@ -3565,17 +4482,19 @@
       <c r="C106" s="6">
         <v>55.094047619047501</v>
       </c>
-      <c r="D106" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E106" s="14" t="s">
+      <c r="D106" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E106" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="8">
         <v>3600</v>
       </c>
-      <c r="H106" s="9"/>
+      <c r="H106" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="107" spans="2:8">
       <c r="B107" s="5">
@@ -3584,7 +4503,7 @@
       <c r="C107" s="6">
         <v>55.625595238095102</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107" s="17">
         <v>2211</v>
       </c>
       <c r="E107" s="7" t="s">
@@ -3605,17 +4524,19 @@
       <c r="C108" s="6">
         <v>56.157142857142702</v>
       </c>
-      <c r="D108" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E108" s="14" t="s">
+      <c r="D108" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E108" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="8">
         <v>5000</v>
       </c>
-      <c r="H108" s="9"/>
+      <c r="H108" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="109" spans="2:8" ht="18" thickBot="1">
       <c r="B109" s="5">
@@ -3624,10 +4545,10 @@
       <c r="C109" s="6">
         <v>56.688690476190402</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D109" s="16">
         <v>5022</v>
       </c>
-      <c r="E109" s="13" t="s">
+      <c r="E109" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F109" s="8">
@@ -3645,17 +4566,19 @@
       <c r="C110" s="6">
         <v>57.220238095238003</v>
       </c>
-      <c r="D110" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E110" s="14" t="s">
+      <c r="D110" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E110" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="8">
         <v>100</v>
       </c>
-      <c r="H110" s="9"/>
+      <c r="H110" s="9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="111" spans="2:8" ht="17.399999999999999">
       <c r="B111" s="5">
@@ -3664,10 +4587,10 @@
       <c r="C111" s="6">
         <v>57.751785714285603</v>
       </c>
-      <c r="D111" s="10">
+      <c r="D111" s="15">
         <v>5015</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E111" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F111" s="8">
@@ -3685,17 +4608,19 @@
       <c r="C112" s="6">
         <v>58.283333333333204</v>
       </c>
-      <c r="D112" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E112" s="14" t="s">
+      <c r="D112" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E112" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F112" s="8"/>
       <c r="G112" s="8">
         <v>2430</v>
       </c>
-      <c r="H112" s="9"/>
+      <c r="H112" s="9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="113" spans="2:8" ht="18" thickBot="1">
       <c r="B113" s="5">
@@ -3704,10 +4629,10 @@
       <c r="C113" s="6">
         <v>58.814880952380797</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="16">
         <v>5002</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E113" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F113" s="8">
@@ -3725,17 +4650,19 @@
       <c r="C114" s="6">
         <v>59.346428571428497</v>
       </c>
-      <c r="D114" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E114" s="14" t="s">
+      <c r="D114" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E114" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F114" s="8"/>
       <c r="G114" s="8">
         <v>1500</v>
       </c>
-      <c r="H114" s="9"/>
+      <c r="H114" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="115" spans="2:8" ht="18" thickBot="1">
       <c r="B115" s="5">
@@ -3744,10 +4671,10 @@
       <c r="C115" s="6">
         <v>59.877976190476097</v>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="16">
         <v>5002</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="E115" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F115" s="8">
@@ -3765,17 +4692,19 @@
       <c r="C116" s="6">
         <v>60.409523809523698</v>
       </c>
-      <c r="D116" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E116" s="14" t="s">
+      <c r="D116" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E116" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="8">
         <v>1000</v>
       </c>
-      <c r="H116" s="9"/>
+      <c r="H116" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="117" spans="2:8" ht="17.399999999999999">
       <c r="B117" s="5">
@@ -3784,10 +4713,10 @@
       <c r="C117" s="6">
         <v>60.941071428571298</v>
       </c>
-      <c r="D117" s="10">
+      <c r="D117" s="15">
         <v>5015</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F117" s="8">
@@ -3805,17 +4734,19 @@
       <c r="C118" s="6">
         <v>61.472619047618899</v>
       </c>
-      <c r="D118" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E118" s="14" t="s">
+      <c r="D118" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E118" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F118" s="8"/>
       <c r="G118" s="8">
         <v>1000</v>
       </c>
-      <c r="H118" s="9"/>
+      <c r="H118" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="119" spans="2:8" ht="18" thickBot="1">
       <c r="B119" s="5">
@@ -3824,10 +4755,10 @@
       <c r="C119" s="6">
         <v>62.004166666666599</v>
       </c>
-      <c r="D119" s="12">
+      <c r="D119" s="16">
         <v>5022</v>
       </c>
-      <c r="E119" s="13" t="s">
+      <c r="E119" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F119" s="8">
@@ -3845,17 +4776,19 @@
       <c r="C120" s="6">
         <v>62.535714285714199</v>
       </c>
-      <c r="D120" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E120" s="14" t="s">
+      <c r="D120" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E120" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F120" s="8"/>
       <c r="G120" s="8">
         <v>500</v>
       </c>
-      <c r="H120" s="9"/>
+      <c r="H120" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="121" spans="2:8" ht="18" thickBot="1">
       <c r="B121" s="5">
@@ -3864,10 +4797,10 @@
       <c r="C121" s="6">
         <v>63.0672619047618</v>
       </c>
-      <c r="D121" s="12">
+      <c r="D121" s="16">
         <v>5022</v>
       </c>
-      <c r="E121" s="13" t="s">
+      <c r="E121" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F121" s="8">
@@ -3885,17 +4818,19 @@
       <c r="C122" s="6">
         <v>63.5988095238094</v>
       </c>
-      <c r="D122" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E122" s="14" t="s">
+      <c r="D122" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E122" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F122" s="8"/>
       <c r="G122" s="8">
         <v>100</v>
       </c>
-      <c r="H122" s="9"/>
+      <c r="H122" s="9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="123" spans="2:8" ht="18" thickBot="1">
       <c r="B123" s="5">
@@ -3904,10 +4839,10 @@
       <c r="C123" s="6">
         <v>64.130357142856994</v>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="16">
         <v>5022</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="E123" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F123" s="8">
@@ -3925,17 +4860,19 @@
       <c r="C124" s="6">
         <v>64.661904761904594</v>
       </c>
-      <c r="D124" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E124" s="14" t="s">
+      <c r="D124" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E124" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F124" s="8"/>
       <c r="G124" s="8">
         <v>500</v>
       </c>
-      <c r="H124" s="9"/>
+      <c r="H124" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="125" spans="2:8">
       <c r="B125" s="5">
@@ -3944,7 +4881,7 @@
       <c r="C125" s="6">
         <v>65.193452380952294</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="17">
         <v>2211</v>
       </c>
       <c r="E125" s="7" t="s">
@@ -3965,17 +4902,19 @@
       <c r="C126" s="6">
         <v>65.724999999999895</v>
       </c>
-      <c r="D126" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E126" s="14" t="s">
+      <c r="D126" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E126" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8">
         <v>5000</v>
       </c>
-      <c r="H126" s="9"/>
+      <c r="H126" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="127" spans="2:8">
       <c r="B127" s="5">
@@ -3984,7 +4923,7 @@
       <c r="C127" s="6">
         <v>66.256547619047495</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="17">
         <v>2212</v>
       </c>
       <c r="E127" s="7" t="s">
@@ -4005,17 +4944,19 @@
       <c r="C128" s="6">
         <v>66.788095238095096</v>
       </c>
-      <c r="D128" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E128" s="14" t="s">
+      <c r="D128" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E128" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F128" s="8"/>
       <c r="G128" s="8">
         <v>5000</v>
       </c>
-      <c r="H128" s="9"/>
+      <c r="H128" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="129" spans="2:8" ht="18" thickBot="1">
       <c r="B129" s="5">
@@ -4024,10 +4965,10 @@
       <c r="C129" s="6">
         <v>67.319642857142696</v>
       </c>
-      <c r="D129" s="12">
+      <c r="D129" s="16">
         <v>5022</v>
       </c>
-      <c r="E129" s="13" t="s">
+      <c r="E129" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F129" s="8">
@@ -4045,17 +4986,19 @@
       <c r="C130" s="6">
         <v>67.851190476190297</v>
       </c>
-      <c r="D130" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E130" s="14" t="s">
+      <c r="D130" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E130" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F130" s="8"/>
       <c r="G130" s="8">
         <v>915</v>
       </c>
-      <c r="H130" s="9"/>
+      <c r="H130" s="9" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="131" spans="2:8" ht="17.399999999999999">
       <c r="B131" s="5">
@@ -4064,10 +5007,10 @@
       <c r="C131" s="6">
         <v>68.382738095237997</v>
       </c>
-      <c r="D131" s="10">
+      <c r="D131" s="15">
         <v>5015</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E131" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F131" s="8">
@@ -4085,17 +5028,19 @@
       <c r="C132" s="6">
         <v>68.914285714285597</v>
       </c>
-      <c r="D132" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E132" s="14" t="s">
+      <c r="D132" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E132" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="8">
         <v>750</v>
       </c>
-      <c r="H132" s="9"/>
+      <c r="H132" s="9" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="133" spans="2:8" ht="18" thickBot="1">
       <c r="B133" s="5">
@@ -4104,10 +5049,10 @@
       <c r="C133" s="6">
         <v>69.445833333333198</v>
       </c>
-      <c r="D133" s="12">
+      <c r="D133" s="16">
         <v>5002</v>
       </c>
-      <c r="E133" s="13" t="s">
+      <c r="E133" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F133" s="8">
@@ -4125,17 +5070,19 @@
       <c r="C134" s="6">
         <v>69.977380952380798</v>
       </c>
-      <c r="D134" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E134" s="14" t="s">
+      <c r="D134" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E134" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F134" s="8"/>
       <c r="G134" s="8">
         <v>1500</v>
       </c>
-      <c r="H134" s="9"/>
+      <c r="H134" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="135" spans="2:8" ht="18" thickBot="1">
       <c r="B135" s="5">
@@ -4144,10 +5091,10 @@
       <c r="C135" s="6">
         <v>70.508928571428399</v>
       </c>
-      <c r="D135" s="12">
+      <c r="D135" s="16">
         <v>5002</v>
       </c>
-      <c r="E135" s="13" t="s">
+      <c r="E135" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F135" s="8">
@@ -4165,17 +5112,19 @@
       <c r="C136" s="6">
         <v>71.040476190476099</v>
       </c>
-      <c r="D136" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E136" s="14" t="s">
+      <c r="D136" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E136" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F136" s="8"/>
       <c r="G136" s="8">
         <v>800</v>
       </c>
-      <c r="H136" s="9"/>
+      <c r="H136" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="137" spans="2:8" ht="18" thickBot="1">
       <c r="B137" s="5">
@@ -4184,10 +5133,10 @@
       <c r="C137" s="6">
         <v>71.572023809523699</v>
       </c>
-      <c r="D137" s="12">
+      <c r="D137" s="16">
         <v>5022</v>
       </c>
-      <c r="E137" s="13" t="s">
+      <c r="E137" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F137" s="8">
@@ -4205,17 +5154,19 @@
       <c r="C138" s="6">
         <v>72.1035714285713</v>
       </c>
-      <c r="D138" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E138" s="14" t="s">
+      <c r="D138" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E138" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F138" s="8"/>
       <c r="G138" s="8">
         <v>400</v>
       </c>
-      <c r="H138" s="9"/>
+      <c r="H138" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="139" spans="2:8" ht="18" thickBot="1">
       <c r="B139" s="5">
@@ -4224,10 +5175,10 @@
       <c r="C139" s="6">
         <v>72.6351190476189</v>
       </c>
-      <c r="D139" s="12">
+      <c r="D139" s="16">
         <v>5022</v>
       </c>
-      <c r="E139" s="13" t="s">
+      <c r="E139" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F139" s="8">
@@ -4245,17 +5196,19 @@
       <c r="C140" s="6">
         <v>73.166666666666501</v>
       </c>
-      <c r="D140" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E140" s="14" t="s">
+      <c r="D140" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E140" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F140" s="8"/>
       <c r="G140" s="8">
         <v>500</v>
       </c>
-      <c r="H140" s="9"/>
+      <c r="H140" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="141" spans="2:8" ht="18" thickBot="1">
       <c r="B141" s="5">
@@ -4264,10 +5217,10 @@
       <c r="C141" s="6">
         <v>73.698214285714101</v>
       </c>
-      <c r="D141" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E141" s="14" t="s">
+      <c r="D141" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E141" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F141" s="8">
@@ -4285,7 +5238,7 @@
       <c r="C142" s="6">
         <v>74.229761904761801</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="17">
         <v>1212</v>
       </c>
       <c r="E142" s="7" t="s">
@@ -4295,7 +5248,9 @@
       <c r="G142" s="8">
         <v>70000</v>
       </c>
-      <c r="H142" s="9"/>
+      <c r="H142" s="9" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="143" spans="2:8">
       <c r="B143" s="5">
@@ -4304,7 +5259,7 @@
       <c r="C143" s="6">
         <v>74.761309523809402</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="17">
         <v>2211</v>
       </c>
       <c r="E143" s="7" t="s">
@@ -4325,17 +5280,19 @@
       <c r="C144" s="6">
         <v>75.292857142857002</v>
       </c>
-      <c r="D144" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E144" s="14" t="s">
+      <c r="D144" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E144" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F144" s="8"/>
       <c r="G144" s="8">
         <v>25000</v>
       </c>
-      <c r="H144" s="9"/>
+      <c r="H144" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="145" spans="2:8">
       <c r="B145" s="5">
@@ -4344,12 +5301,11 @@
       <c r="C145" s="6">
         <v>75.824404761904603</v>
       </c>
-      <c r="D145" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E145" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D145,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D145" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F145" s="8">
         <v>550</v>
@@ -4366,17 +5322,19 @@
       <c r="C146" s="6">
         <v>76.355952380952203</v>
       </c>
-      <c r="D146" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E146" s="14" t="s">
+      <c r="D146" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E146" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F146" s="8"/>
       <c r="G146" s="8">
         <v>550</v>
       </c>
-      <c r="H146" s="9"/>
+      <c r="H146" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="147" spans="2:8" ht="18" thickBot="1">
       <c r="B147" s="5">
@@ -4385,10 +5343,10 @@
       <c r="C147" s="6">
         <v>76.887499999999903</v>
       </c>
-      <c r="D147" s="12">
+      <c r="D147" s="16">
         <v>5022</v>
       </c>
-      <c r="E147" s="13" t="s">
+      <c r="E147" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F147" s="8">
@@ -4406,17 +5364,19 @@
       <c r="C148" s="6">
         <v>77.419047619047504</v>
       </c>
-      <c r="D148" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E148" s="14" t="s">
+      <c r="D148" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E148" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F148" s="8"/>
       <c r="G148" s="8">
         <v>500</v>
       </c>
-      <c r="H148" s="9"/>
+      <c r="H148" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="149" spans="2:8" ht="17.399999999999999">
       <c r="B149" s="5">
@@ -4425,10 +5385,10 @@
       <c r="C149" s="6">
         <v>77.950595238095104</v>
       </c>
-      <c r="D149" s="10">
+      <c r="D149" s="15">
         <v>5015</v>
       </c>
-      <c r="E149" s="11" t="s">
+      <c r="E149" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F149" s="8">
@@ -4446,17 +5406,19 @@
       <c r="C150" s="6">
         <v>78.482142857142705</v>
       </c>
-      <c r="D150" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E150" s="14" t="s">
+      <c r="D150" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E150" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F150" s="8"/>
       <c r="G150" s="8">
         <v>500</v>
       </c>
-      <c r="H150" s="9"/>
+      <c r="H150" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="151" spans="2:8" ht="17.399999999999999">
       <c r="B151" s="5">
@@ -4465,10 +5427,10 @@
       <c r="C151" s="6">
         <v>79.013690476190305</v>
       </c>
-      <c r="D151" s="10">
+      <c r="D151" s="15">
         <v>5015</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F151" s="8">
@@ -4486,17 +5448,19 @@
       <c r="C152" s="6">
         <v>79.545238095237906</v>
       </c>
-      <c r="D152" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E152" s="14" t="s">
+      <c r="D152" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E152" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F152" s="8"/>
       <c r="G152" s="8">
         <v>500</v>
       </c>
-      <c r="H152" s="9"/>
+      <c r="H152" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="153" spans="2:8">
       <c r="B153" s="5">
@@ -4505,7 +5469,7 @@
       <c r="C153" s="6">
         <v>80.076785714285606</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D153" s="17">
         <v>2211</v>
       </c>
       <c r="E153" s="7" t="s">
@@ -4526,17 +5490,19 @@
       <c r="C154" s="6">
         <v>80.608333333333206</v>
       </c>
-      <c r="D154" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E154" s="14" t="s">
+      <c r="D154" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E154" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="8">
         <v>10000</v>
       </c>
-      <c r="H154" s="9"/>
+      <c r="H154" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="155" spans="2:8" ht="17.399999999999999">
       <c r="B155" s="5">
@@ -4545,10 +5511,10 @@
       <c r="C155" s="6">
         <v>81.139880952380807</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="17">
         <v>5003</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E155" s="10" t="s">
         <v>99</v>
       </c>
       <c r="F155" s="8">
@@ -4566,17 +5532,19 @@
       <c r="C156" s="6">
         <v>81.671428571428393</v>
       </c>
-      <c r="D156" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E156" s="14" t="s">
+      <c r="D156" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E156" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F156" s="8"/>
       <c r="G156" s="8">
         <v>2000</v>
       </c>
-      <c r="H156" s="9"/>
+      <c r="H156" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="157" spans="2:8" ht="17.399999999999999">
       <c r="B157" s="5">
@@ -4585,10 +5553,10 @@
       <c r="C157" s="6">
         <v>82.202976190475994</v>
       </c>
-      <c r="D157" s="10">
+      <c r="D157" s="15">
         <v>5015</v>
       </c>
-      <c r="E157" s="11" t="s">
+      <c r="E157" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F157" s="8">
@@ -4606,17 +5574,19 @@
       <c r="C158" s="6">
         <v>82.734523809523594</v>
       </c>
-      <c r="D158" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E158" s="14" t="s">
+      <c r="D158" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E158" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8">
         <v>1000</v>
       </c>
-      <c r="H158" s="9"/>
+      <c r="H158" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="159" spans="2:8" ht="17.399999999999999">
       <c r="B159" s="5">
@@ -4625,10 +5595,10 @@
       <c r="C159" s="6">
         <v>83.266071428571294</v>
       </c>
-      <c r="D159" s="10">
+      <c r="D159" s="15">
         <v>5015</v>
       </c>
-      <c r="E159" s="11" t="s">
+      <c r="E159" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F159" s="8">
@@ -4646,17 +5616,19 @@
       <c r="C160" s="6">
         <v>83.797619047618895</v>
       </c>
-      <c r="D160" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E160" s="14" t="s">
+      <c r="D160" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E160" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="8">
         <v>1000</v>
       </c>
-      <c r="H160" s="9"/>
+      <c r="H160" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="161" spans="2:8">
       <c r="B161" s="5">
@@ -4665,7 +5637,7 @@
       <c r="C161" s="6">
         <v>84.329166666666495</v>
       </c>
-      <c r="D161" s="6">
+      <c r="D161" s="17">
         <v>2211</v>
       </c>
       <c r="E161" s="7" t="s">
@@ -4686,17 +5658,19 @@
       <c r="C162" s="6">
         <v>84.860714285714096</v>
       </c>
-      <c r="D162" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E162" s="14" t="s">
+      <c r="D162" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E162" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="8">
         <v>12000</v>
       </c>
-      <c r="H162" s="9"/>
+      <c r="H162" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="163" spans="2:8" ht="18" thickBot="1">
       <c r="B163" s="5">
@@ -4705,10 +5679,10 @@
       <c r="C163" s="6">
         <v>85.392261904761696</v>
       </c>
-      <c r="D163" s="12">
+      <c r="D163" s="16">
         <v>5022</v>
       </c>
-      <c r="E163" s="13" t="s">
+      <c r="E163" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F163" s="8">
@@ -4726,17 +5700,19 @@
       <c r="C164" s="6">
         <v>85.923809523809396</v>
       </c>
-      <c r="D164" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E164" s="14" t="s">
+      <c r="D164" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E164" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="8">
         <v>5090</v>
       </c>
-      <c r="H164" s="9"/>
+      <c r="H164" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="165" spans="2:8">
       <c r="B165" s="5">
@@ -4745,12 +5721,11 @@
       <c r="C165" s="6">
         <v>86.455357142856997</v>
       </c>
-      <c r="D165" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E165" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D165,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D165" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E165" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F165" s="8">
         <v>2850</v>
@@ -4767,17 +5742,19 @@
       <c r="C166" s="6">
         <v>86.986904761904597</v>
       </c>
-      <c r="D166" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E166" s="14" t="s">
+      <c r="D166" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E166" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="8">
         <v>2850</v>
       </c>
-      <c r="H166" s="9"/>
+      <c r="H166" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="167" spans="2:8" ht="18" thickBot="1">
       <c r="B167" s="5">
@@ -4786,10 +5763,10 @@
       <c r="C167" s="6">
         <v>87.518452380952198</v>
       </c>
-      <c r="D167" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E167" s="14" t="s">
+      <c r="D167" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E167" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F167" s="8">
@@ -4807,7 +5784,7 @@
       <c r="C168" s="6">
         <v>88.049999999999798</v>
       </c>
-      <c r="D168" s="6">
+      <c r="D168" s="17">
         <v>1213</v>
       </c>
       <c r="E168" s="7" t="s">
@@ -4828,12 +5805,11 @@
       <c r="C169" s="6">
         <v>88.581547619047498</v>
       </c>
-      <c r="D169" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E169" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D169,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D169" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E169" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F169" s="8">
         <v>4050</v>
@@ -4850,17 +5826,19 @@
       <c r="C170" s="6">
         <v>89.113095238095099</v>
       </c>
-      <c r="D170" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E170" s="14" t="s">
+      <c r="D170" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E170" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="8">
         <v>4050</v>
       </c>
-      <c r="H170" s="9"/>
+      <c r="H170" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="171" spans="2:8">
       <c r="B171" s="5">
@@ -4869,7 +5847,7 @@
       <c r="C171" s="6">
         <v>89.644642857142699</v>
       </c>
-      <c r="D171" s="6">
+      <c r="D171" s="17">
         <v>2211</v>
       </c>
       <c r="E171" s="7" t="s">
@@ -4890,17 +5868,19 @@
       <c r="C172" s="6">
         <v>90.1761904761903</v>
       </c>
-      <c r="D172" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E172" s="14" t="s">
+      <c r="D172" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E172" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="8">
         <v>15000</v>
       </c>
-      <c r="H172" s="9"/>
+      <c r="H172" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="173" spans="2:8" ht="18" thickBot="1">
       <c r="B173" s="5">
@@ -4909,10 +5889,10 @@
       <c r="C173" s="6">
         <v>90.7077380952379</v>
       </c>
-      <c r="D173" s="12">
+      <c r="D173" s="16">
         <v>5002</v>
       </c>
-      <c r="E173" s="13" t="s">
+      <c r="E173" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F173" s="8">
@@ -4930,17 +5910,19 @@
       <c r="C174" s="6">
         <v>91.239285714285501</v>
       </c>
-      <c r="D174" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E174" s="14" t="s">
+      <c r="D174" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E174" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F174" s="8"/>
       <c r="G174" s="8">
         <v>200</v>
       </c>
-      <c r="H174" s="9"/>
+      <c r="H174" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="175" spans="2:8" ht="17.399999999999999">
       <c r="B175" s="5">
@@ -4949,10 +5931,10 @@
       <c r="C175" s="6">
         <v>91.770833333333201</v>
       </c>
-      <c r="D175" s="10">
+      <c r="D175" s="15">
         <v>5015</v>
       </c>
-      <c r="E175" s="11" t="s">
+      <c r="E175" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F175" s="8">
@@ -4970,17 +5952,19 @@
       <c r="C176" s="6">
         <v>92.302380952380801</v>
       </c>
-      <c r="D176" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E176" s="14" t="s">
+      <c r="D176" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E176" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F176" s="8"/>
       <c r="G176" s="8">
         <v>500</v>
       </c>
-      <c r="H176" s="9"/>
+      <c r="H176" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="177" spans="2:8" ht="17.399999999999999">
       <c r="B177" s="5">
@@ -4989,10 +5973,10 @@
       <c r="C177" s="6">
         <v>92.833928571428402</v>
       </c>
-      <c r="D177" s="10">
+      <c r="D177" s="15">
         <v>5015</v>
       </c>
-      <c r="E177" s="11" t="s">
+      <c r="E177" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F177" s="8">
@@ -5010,17 +5994,19 @@
       <c r="C178" s="6">
         <v>93.365476190476002</v>
       </c>
-      <c r="D178" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E178" s="14" t="s">
+      <c r="D178" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E178" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F178" s="8"/>
       <c r="G178" s="8">
         <v>1000</v>
       </c>
-      <c r="H178" s="9"/>
+      <c r="H178" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="179" spans="2:8" ht="17.399999999999999">
       <c r="B179" s="5">
@@ -5029,10 +6015,10 @@
       <c r="C179" s="6">
         <v>93.897023809523603</v>
       </c>
-      <c r="D179" s="10">
+      <c r="D179" s="15">
         <v>5015</v>
       </c>
-      <c r="E179" s="11" t="s">
+      <c r="E179" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F179" s="8">
@@ -5050,17 +6036,19 @@
       <c r="C180" s="6">
         <v>94.428571428571303</v>
       </c>
-      <c r="D180" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E180" s="14" t="s">
+      <c r="D180" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E180" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F180" s="8"/>
       <c r="G180" s="8">
         <v>450</v>
       </c>
-      <c r="H180" s="9"/>
+      <c r="H180" s="9" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="181" spans="2:8" ht="17.399999999999999">
       <c r="B181" s="5">
@@ -5069,10 +6057,10 @@
       <c r="C181" s="6">
         <v>94.960119047618903</v>
       </c>
-      <c r="D181" s="10">
+      <c r="D181" s="15">
         <v>5015</v>
       </c>
-      <c r="E181" s="11" t="s">
+      <c r="E181" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F181" s="8">
@@ -5090,17 +6078,19 @@
       <c r="C182" s="6">
         <v>95.491666666666504</v>
       </c>
-      <c r="D182" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E182" s="14" t="s">
+      <c r="D182" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E182" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F182" s="8"/>
       <c r="G182" s="8">
         <v>1000</v>
       </c>
-      <c r="H182" s="9"/>
+      <c r="H182" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="183" spans="2:8">
       <c r="B183" s="5">
@@ -5109,7 +6099,7 @@
       <c r="C183" s="6">
         <v>96.023214285714104</v>
       </c>
-      <c r="D183" s="6">
+      <c r="D183" s="17">
         <v>2211</v>
       </c>
       <c r="E183" s="7" t="s">
@@ -5130,17 +6120,19 @@
       <c r="C184" s="6">
         <v>96.554761904761705</v>
       </c>
-      <c r="D184" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E184" s="14" t="s">
+      <c r="D184" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E184" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F184" s="8"/>
       <c r="G184" s="8">
         <v>15000</v>
       </c>
-      <c r="H184" s="9"/>
+      <c r="H184" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="185" spans="2:8">
       <c r="B185" s="5">
@@ -5149,12 +6141,11 @@
       <c r="C185" s="6">
         <v>97.086309523809305</v>
       </c>
-      <c r="D185" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E185" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D185,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D185" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E185" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F185" s="8">
         <v>2100</v>
@@ -5171,17 +6162,19 @@
       <c r="C186" s="6">
         <v>97.617857142857005</v>
       </c>
-      <c r="D186" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E186" s="14" t="s">
+      <c r="D186" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E186" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F186" s="8"/>
       <c r="G186" s="8">
         <v>2100</v>
       </c>
-      <c r="H186" s="9"/>
+      <c r="H186" s="9" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="187" spans="2:8" ht="18" thickBot="1">
       <c r="B187" s="5">
@@ -5190,10 +6183,10 @@
       <c r="C187" s="6">
         <v>98.149404761904606</v>
       </c>
-      <c r="D187" s="12">
+      <c r="D187" s="16">
         <v>5022</v>
       </c>
-      <c r="E187" s="13" t="s">
+      <c r="E187" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F187" s="8">
@@ -5211,17 +6204,19 @@
       <c r="C188" s="6">
         <v>98.680952380952206</v>
       </c>
-      <c r="D188" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E188" s="14" t="s">
+      <c r="D188" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E188" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F188" s="8"/>
       <c r="G188" s="8">
         <v>300</v>
       </c>
-      <c r="H188" s="9"/>
+      <c r="H188" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="189" spans="2:8">
       <c r="B189" s="5">
@@ -5230,7 +6225,7 @@
       <c r="C189" s="6">
         <v>99.212499999999807</v>
       </c>
-      <c r="D189" s="6">
+      <c r="D189" s="17">
         <v>2212</v>
       </c>
       <c r="E189" s="7" t="s">
@@ -5251,17 +6246,19 @@
       <c r="C190" s="6">
         <v>99.744047619047393</v>
       </c>
-      <c r="D190" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E190" s="14" t="s">
+      <c r="D190" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E190" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="8">
         <v>12673</v>
       </c>
-      <c r="H190" s="9"/>
+      <c r="H190" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="191" spans="2:8">
       <c r="B191" s="5">
@@ -5270,7 +6267,7 @@
       <c r="C191" s="6">
         <v>100.27559523809499</v>
       </c>
-      <c r="D191" s="6">
+      <c r="D191" s="17">
         <v>2213</v>
       </c>
       <c r="E191" s="7" t="s">
@@ -5291,17 +6288,19 @@
       <c r="C192" s="6">
         <v>100.80714285714301</v>
       </c>
-      <c r="D192" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E192" s="14" t="s">
+      <c r="D192" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E192" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="8">
         <v>27206</v>
       </c>
-      <c r="H192" s="9"/>
+      <c r="H192" s="9" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="193" spans="2:8" ht="18" thickBot="1">
       <c r="B193" s="5">
@@ -5310,10 +6309,10 @@
       <c r="C193" s="6">
         <v>101.33869047619</v>
       </c>
-      <c r="D193" s="12">
+      <c r="D193" s="16">
         <v>5022</v>
       </c>
-      <c r="E193" s="13" t="s">
+      <c r="E193" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F193" s="8">
@@ -5331,17 +6330,19 @@
       <c r="C194" s="6">
         <v>101.87023809523799</v>
       </c>
-      <c r="D194" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E194" s="14" t="s">
+      <c r="D194" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E194" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="8">
         <v>1550</v>
       </c>
-      <c r="H194" s="9"/>
+      <c r="H194" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="195" spans="2:8" ht="17.399999999999999">
       <c r="B195" s="5">
@@ -5350,10 +6351,10 @@
       <c r="C195" s="6">
         <v>102.40178571428601</v>
       </c>
-      <c r="D195" s="10">
+      <c r="D195" s="15">
         <v>5015</v>
       </c>
-      <c r="E195" s="11" t="s">
+      <c r="E195" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F195" s="8">
@@ -5371,17 +6372,19 @@
       <c r="C196" s="6">
         <v>102.933333333333</v>
       </c>
-      <c r="D196" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E196" s="14" t="s">
+      <c r="D196" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E196" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="8">
         <v>1500</v>
       </c>
-      <c r="H196" s="9"/>
+      <c r="H196" s="9" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="197" spans="2:8" ht="18" thickBot="1">
       <c r="B197" s="5">
@@ -5390,10 +6393,10 @@
       <c r="C197" s="6">
         <v>103.46488095238099</v>
       </c>
-      <c r="D197" s="12">
+      <c r="D197" s="16">
         <v>5002</v>
       </c>
-      <c r="E197" s="13" t="s">
+      <c r="E197" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F197" s="8">
@@ -5411,17 +6414,19 @@
       <c r="C198" s="6">
         <v>103.996428571428</v>
       </c>
-      <c r="D198" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E198" s="14" t="s">
+      <c r="D198" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E198" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="8">
         <v>3000</v>
       </c>
-      <c r="H198" s="9"/>
+      <c r="H198" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="199" spans="2:8" ht="18" thickBot="1">
       <c r="B199" s="5">
@@ -5430,10 +6435,10 @@
       <c r="C199" s="6">
         <v>104.527976190476</v>
       </c>
-      <c r="D199" s="12">
+      <c r="D199" s="16">
         <v>5002</v>
       </c>
-      <c r="E199" s="13" t="s">
+      <c r="E199" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F199" s="8">
@@ -5451,17 +6456,19 @@
       <c r="C200" s="6">
         <v>105.05952380952399</v>
       </c>
-      <c r="D200" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E200" s="14" t="s">
+      <c r="D200" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E200" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="8">
         <v>800</v>
       </c>
-      <c r="H200" s="9"/>
+      <c r="H200" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="201" spans="2:8" ht="17.399999999999999">
       <c r="B201" s="5">
@@ -5470,10 +6477,10 @@
       <c r="C201" s="6">
         <v>105.591071428571</v>
       </c>
-      <c r="D201" s="10">
+      <c r="D201" s="15">
         <v>5015</v>
       </c>
-      <c r="E201" s="11" t="s">
+      <c r="E201" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F201" s="8">
@@ -5491,17 +6498,19 @@
       <c r="C202" s="6">
         <v>106.122619047619</v>
       </c>
-      <c r="D202" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E202" s="14" t="s">
+      <c r="D202" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E202" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="8">
         <v>1000</v>
       </c>
-      <c r="H202" s="9"/>
+      <c r="H202" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="203" spans="2:8" ht="18" thickBot="1">
       <c r="B203" s="5">
@@ -5510,10 +6519,10 @@
       <c r="C203" s="6">
         <v>106.654166666667</v>
       </c>
-      <c r="D203" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E203" s="14" t="s">
+      <c r="D203" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E203" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F203" s="8">
@@ -5531,7 +6540,7 @@
       <c r="C204" s="6">
         <v>107.185714285714</v>
       </c>
-      <c r="D204" s="6">
+      <c r="D204" s="17">
         <v>1211</v>
       </c>
       <c r="E204" s="7" t="s">
@@ -5552,10 +6561,10 @@
       <c r="C205" s="6">
         <v>107.717261904762</v>
       </c>
-      <c r="D205" s="12">
+      <c r="D205" s="16">
         <v>5022</v>
       </c>
-      <c r="E205" s="13" t="s">
+      <c r="E205" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F205" s="8">
@@ -5573,17 +6582,19 @@
       <c r="C206" s="6">
         <v>108.24880952381</v>
       </c>
-      <c r="D206" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E206" s="14" t="s">
+      <c r="D206" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E206" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="8">
         <v>250</v>
       </c>
-      <c r="H206" s="9"/>
+      <c r="H206" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="207" spans="2:8" ht="17.399999999999999">
       <c r="B207" s="5">
@@ -5592,10 +6603,10 @@
       <c r="C207" s="6">
         <v>108.780357142857</v>
       </c>
-      <c r="D207" s="10">
+      <c r="D207" s="15">
         <v>5015</v>
       </c>
-      <c r="E207" s="11" t="s">
+      <c r="E207" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F207" s="8">
@@ -5613,17 +6624,19 @@
       <c r="C208" s="6">
         <v>109.311904761905</v>
       </c>
-      <c r="D208" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E208" s="14" t="s">
+      <c r="D208" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E208" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F208" s="8"/>
       <c r="G208" s="8">
         <v>3000</v>
       </c>
-      <c r="H208" s="9"/>
+      <c r="H208" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="209" spans="2:8">
       <c r="B209" s="5">
@@ -5632,7 +6645,7 @@
       <c r="C209" s="6">
         <v>109.843452380952</v>
       </c>
-      <c r="D209" s="6">
+      <c r="D209" s="17">
         <v>2212</v>
       </c>
       <c r="E209" s="7" t="s">
@@ -5653,17 +6666,19 @@
       <c r="C210" s="6">
         <v>110.375</v>
       </c>
-      <c r="D210" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E210" s="14" t="s">
+      <c r="D210" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E210" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F210" s="8"/>
       <c r="G210" s="8">
         <v>6775</v>
       </c>
-      <c r="H210" s="9"/>
+      <c r="H210" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="211" spans="2:8">
       <c r="B211" s="5">
@@ -5672,12 +6687,11 @@
       <c r="C211" s="6">
         <v>110.906547619048</v>
       </c>
-      <c r="D211" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E211" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D211,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D211" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E211" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F211" s="8">
         <v>5875</v>
@@ -5694,17 +6708,19 @@
       <c r="C212" s="6">
         <v>111.438095238095</v>
       </c>
-      <c r="D212" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E212" s="14" t="s">
+      <c r="D212" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E212" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F212" s="8"/>
       <c r="G212" s="8">
         <v>5875</v>
       </c>
-      <c r="H212" s="9"/>
+      <c r="H212" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="213" spans="2:8">
       <c r="B213" s="5">
@@ -5713,7 +6729,7 @@
       <c r="C213" s="6">
         <v>111.969642857143</v>
       </c>
-      <c r="D213" s="6">
+      <c r="D213" s="17">
         <v>2211</v>
       </c>
       <c r="E213" s="7" t="s">
@@ -5734,17 +6750,19 @@
       <c r="C214" s="6">
         <v>112.50119047619</v>
       </c>
-      <c r="D214" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E214" s="14" t="s">
+      <c r="D214" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E214" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F214" s="8"/>
       <c r="G214" s="8">
         <v>15000</v>
       </c>
-      <c r="H214" s="9"/>
+      <c r="H214" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="215" spans="2:8" ht="17.399999999999999">
       <c r="B215" s="5">
@@ -5753,10 +6771,10 @@
       <c r="C215" s="6">
         <v>113.032738095238</v>
       </c>
-      <c r="D215" s="10">
+      <c r="D215" s="15">
         <v>5015</v>
       </c>
-      <c r="E215" s="11" t="s">
+      <c r="E215" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F215" s="8">
@@ -5774,17 +6792,19 @@
       <c r="C216" s="6">
         <v>113.564285714286</v>
       </c>
-      <c r="D216" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E216" s="14" t="s">
+      <c r="D216" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E216" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F216" s="8"/>
       <c r="G216" s="8">
         <v>5000</v>
       </c>
-      <c r="H216" s="9"/>
+      <c r="H216" s="9" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="217" spans="2:8">
       <c r="B217" s="5">
@@ -5793,12 +6813,11 @@
       <c r="C217" s="6">
         <v>114.095833333333</v>
       </c>
-      <c r="D217" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E217" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D217,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D217" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E217" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F217" s="8">
         <v>1875</v>
@@ -5815,17 +6834,19 @@
       <c r="C218" s="6">
         <v>114.627380952381</v>
       </c>
-      <c r="D218" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E218" s="14" t="s">
+      <c r="D218" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E218" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F218" s="8"/>
       <c r="G218" s="8">
         <v>1875</v>
       </c>
-      <c r="H218" s="9"/>
+      <c r="H218" s="9" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="219" spans="2:8" ht="18" thickBot="1">
       <c r="B219" s="5">
@@ -5834,10 +6855,10 @@
       <c r="C219" s="6">
         <v>115.158928571429</v>
       </c>
-      <c r="D219" s="12">
+      <c r="D219" s="16">
         <v>5002</v>
       </c>
-      <c r="E219" s="13" t="s">
+      <c r="E219" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F219" s="8">
@@ -5855,17 +6876,19 @@
       <c r="C220" s="6">
         <v>115.69047619047601</v>
       </c>
-      <c r="D220" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E220" s="14" t="s">
+      <c r="D220" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E220" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F220" s="8"/>
       <c r="G220" s="8">
         <v>1500</v>
       </c>
-      <c r="H220" s="9"/>
+      <c r="H220" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="221" spans="2:8" ht="18" thickBot="1">
       <c r="B221" s="5">
@@ -5874,10 +6897,10 @@
       <c r="C221" s="6">
         <v>116.222023809524</v>
       </c>
-      <c r="D221" s="12">
+      <c r="D221" s="16">
         <v>5002</v>
       </c>
-      <c r="E221" s="13" t="s">
+      <c r="E221" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F221" s="8">
@@ -5895,17 +6918,19 @@
       <c r="C222" s="6">
         <v>116.75357142857099</v>
       </c>
-      <c r="D222" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E222" s="14" t="s">
+      <c r="D222" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E222" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F222" s="8"/>
       <c r="G222" s="8">
         <v>1350</v>
       </c>
-      <c r="H222" s="9"/>
+      <c r="H222" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="223" spans="2:8" ht="18" thickBot="1">
       <c r="B223" s="5">
@@ -5914,10 +6939,10 @@
       <c r="C223" s="6">
         <v>117.28511904761901</v>
       </c>
-      <c r="D223" s="12">
+      <c r="D223" s="16">
         <v>5002</v>
       </c>
-      <c r="E223" s="13" t="s">
+      <c r="E223" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F223" s="8">
@@ -5935,17 +6960,19 @@
       <c r="C224" s="6">
         <v>117.816666666667</v>
       </c>
-      <c r="D224" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E224" s="14" t="s">
+      <c r="D224" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E224" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F224" s="8"/>
       <c r="G224" s="8">
         <v>1000</v>
       </c>
-      <c r="H224" s="9"/>
+      <c r="H224" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="225" spans="2:8" ht="18" thickBot="1">
       <c r="B225" s="5">
@@ -5954,10 +6981,10 @@
       <c r="C225" s="6">
         <v>118.34821428571399</v>
       </c>
-      <c r="D225" s="12">
+      <c r="D225" s="16">
         <v>5002</v>
       </c>
-      <c r="E225" s="13" t="s">
+      <c r="E225" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F225" s="8">
@@ -5975,17 +7002,19 @@
       <c r="C226" s="6">
         <v>118.87976190476201</v>
       </c>
-      <c r="D226" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E226" s="14" t="s">
+      <c r="D226" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E226" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F226" s="8"/>
       <c r="G226" s="8">
         <v>2200</v>
       </c>
-      <c r="H226" s="9"/>
+      <c r="H226" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="227" spans="2:8" ht="18" thickBot="1">
       <c r="B227" s="5">
@@ -5994,10 +7023,10 @@
       <c r="C227" s="6">
         <v>119.41130952381</v>
       </c>
-      <c r="D227" s="12">
+      <c r="D227" s="16">
         <v>5002</v>
       </c>
-      <c r="E227" s="13" t="s">
+      <c r="E227" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F227" s="8">
@@ -6015,17 +7044,19 @@
       <c r="C228" s="6">
         <v>119.94285714285699</v>
       </c>
-      <c r="D228" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E228" s="14" t="s">
+      <c r="D228" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E228" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F228" s="8"/>
       <c r="G228" s="8">
         <v>1000</v>
       </c>
-      <c r="H228" s="9"/>
+      <c r="H228" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="229" spans="2:8" ht="18" thickBot="1">
       <c r="B229" s="5">
@@ -6034,10 +7065,10 @@
       <c r="C229" s="6">
         <v>120.47440476190501</v>
       </c>
-      <c r="D229" s="12">
+      <c r="D229" s="16">
         <v>5022</v>
       </c>
-      <c r="E229" s="13" t="s">
+      <c r="E229" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F229" s="8">
@@ -6055,17 +7086,19 @@
       <c r="C230" s="6">
         <v>121.005952380952</v>
       </c>
-      <c r="D230" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E230" s="14" t="s">
+      <c r="D230" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E230" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F230" s="8"/>
       <c r="G230" s="8">
         <v>340</v>
       </c>
-      <c r="H230" s="9"/>
+      <c r="H230" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="231" spans="2:8" ht="18" thickBot="1">
       <c r="B231" s="5">
@@ -6074,10 +7107,10 @@
       <c r="C231" s="6">
         <v>121.53749999999999</v>
       </c>
-      <c r="D231" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E231" s="14" t="s">
+      <c r="D231" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E231" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F231" s="8">
@@ -6095,7 +7128,7 @@
       <c r="C232" s="6">
         <v>122.06904761904801</v>
       </c>
-      <c r="D232" s="6">
+      <c r="D232" s="17">
         <v>1211</v>
       </c>
       <c r="E232" s="7" t="s">
@@ -6116,10 +7149,10 @@
       <c r="C233" s="6">
         <v>122.600595238095</v>
       </c>
-      <c r="D233" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E233" s="14" t="s">
+      <c r="D233" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E233" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F233" s="8">
@@ -6137,7 +7170,7 @@
       <c r="C234" s="6">
         <v>123.13214285714299</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="17">
         <v>1213</v>
       </c>
       <c r="E234" s="7" t="s">
@@ -6158,10 +7191,10 @@
       <c r="C235" s="6">
         <v>123.66369047619</v>
       </c>
-      <c r="D235" s="10">
+      <c r="D235" s="15">
         <v>5015</v>
       </c>
-      <c r="E235" s="11" t="s">
+      <c r="E235" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F235" s="8">
@@ -6179,17 +7212,19 @@
       <c r="C236" s="6">
         <v>124.195238095238</v>
       </c>
-      <c r="D236" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E236" s="14" t="s">
+      <c r="D236" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E236" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F236" s="8"/>
       <c r="G236" s="8">
         <v>4425</v>
       </c>
-      <c r="H236" s="9"/>
+      <c r="H236" s="9" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="237" spans="2:8" ht="17.399999999999999">
       <c r="B237" s="5">
@@ -6198,10 +7233,10 @@
       <c r="C237" s="6">
         <v>124.726785714286</v>
       </c>
-      <c r="D237" s="10">
+      <c r="D237" s="15">
         <v>5015</v>
       </c>
-      <c r="E237" s="11" t="s">
+      <c r="E237" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F237" s="8">
@@ -6219,17 +7254,19 @@
       <c r="C238" s="6">
         <v>125.258333333333</v>
       </c>
-      <c r="D238" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E238" s="14" t="s">
+      <c r="D238" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E238" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F238" s="8"/>
       <c r="G238" s="8">
         <v>3000</v>
       </c>
-      <c r="H238" s="9"/>
+      <c r="H238" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="239" spans="2:8" ht="17.399999999999999">
       <c r="B239" s="5">
@@ -6238,10 +7275,10 @@
       <c r="C239" s="6">
         <v>125.789880952381</v>
       </c>
-      <c r="D239" s="10">
+      <c r="D239" s="15">
         <v>5015</v>
       </c>
-      <c r="E239" s="11" t="s">
+      <c r="E239" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F239" s="8">
@@ -6259,17 +7296,19 @@
       <c r="C240" s="6">
         <v>126.321428571429</v>
       </c>
-      <c r="D240" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E240" s="14" t="s">
+      <c r="D240" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E240" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F240" s="8"/>
       <c r="G240" s="8">
         <v>12000</v>
       </c>
-      <c r="H240" s="9"/>
+      <c r="H240" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="241" spans="2:8" ht="18" thickBot="1">
       <c r="B241" s="5">
@@ -6278,10 +7317,10 @@
       <c r="C241" s="6">
         <v>126.852976190476</v>
       </c>
-      <c r="D241" s="12">
+      <c r="D241" s="16">
         <v>5022</v>
       </c>
-      <c r="E241" s="13" t="s">
+      <c r="E241" s="11" t="s">
         <v>101</v>
       </c>
       <c r="F241" s="8">
@@ -6299,31 +7338,32 @@
       <c r="C242" s="6">
         <v>127.384523809524</v>
       </c>
-      <c r="D242" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E242" s="14" t="s">
+      <c r="D242" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E242" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F242" s="8"/>
       <c r="G242" s="8">
         <v>100</v>
       </c>
-      <c r="H242" s="9"/>
-    </row>
-    <row r="243" spans="2:8">
+      <c r="H242" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="243" spans="2:8" ht="17.399999999999999">
       <c r="B243" s="5">
         <v>46219</v>
       </c>
       <c r="C243" s="6">
         <v>127.916071428571</v>
       </c>
-      <c r="D243" s="6">
+      <c r="D243" s="17">
         <v>3001</v>
       </c>
-      <c r="E243" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D243,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v/>
+      <c r="E243" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="F243" s="8">
         <v>5170</v>
@@ -6340,10 +7380,10 @@
       <c r="C244" s="6">
         <v>128.44761904761901</v>
       </c>
-      <c r="D244" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E244" s="14" t="s">
+      <c r="D244" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E244" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F244" s="8"/>
@@ -6361,10 +7401,10 @@
       <c r="C245" s="6">
         <v>128.979166666667</v>
       </c>
-      <c r="D245" s="12">
+      <c r="D245" s="16">
         <v>5002</v>
       </c>
-      <c r="E245" s="13" t="s">
+      <c r="E245" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F245" s="8">
@@ -6382,17 +7422,19 @@
       <c r="C246" s="6">
         <v>129.51071428571399</v>
       </c>
-      <c r="D246" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E246" s="14" t="s">
+      <c r="D246" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E246" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F246" s="8"/>
       <c r="G246" s="8">
         <v>5400</v>
       </c>
-      <c r="H246" s="9"/>
+      <c r="H246" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="247" spans="2:8" ht="18" thickBot="1">
       <c r="B247" s="5">
@@ -6401,10 +7443,10 @@
       <c r="C247" s="6">
         <v>130.042261904762</v>
       </c>
-      <c r="D247" s="12">
+      <c r="D247" s="16">
         <v>5002</v>
       </c>
-      <c r="E247" s="13" t="s">
+      <c r="E247" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F247" s="8">
@@ -6422,17 +7464,19 @@
       <c r="C248" s="6">
         <v>130.57380952380899</v>
       </c>
-      <c r="D248" s="10">
-        <v>1111</v>
-      </c>
-      <c r="E248" s="14" t="s">
+      <c r="D248" s="15">
+        <v>1111</v>
+      </c>
+      <c r="E248" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F248" s="8"/>
       <c r="G248" s="8">
         <v>800</v>
       </c>
-      <c r="H248" s="9"/>
+      <c r="H248" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="249" spans="2:8">
       <c r="B249" s="5">
@@ -6441,12 +7485,11 @@
       <c r="C249" s="6">
         <v>131.105357142857</v>
       </c>
-      <c r="D249" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E249" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D249,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D249" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E249" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F249" s="8">
         <v>2897</v>
@@ -6463,7 +7506,7 @@
       <c r="C250" s="6">
         <v>131.63690476190499</v>
       </c>
-      <c r="D250" s="6">
+      <c r="D250" s="17">
         <v>2212</v>
       </c>
       <c r="E250" s="7" t="s">
@@ -6484,12 +7527,11 @@
       <c r="C251" s="6">
         <v>132.168452380952</v>
       </c>
-      <c r="D251" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E251" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D251,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D251" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E251" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F251" s="8">
         <v>1050</v>
@@ -6506,7 +7548,7 @@
       <c r="C252" s="6">
         <v>132.69999999999999</v>
       </c>
-      <c r="D252" s="6">
+      <c r="D252" s="17">
         <v>2212</v>
       </c>
       <c r="E252" s="7" t="s">
@@ -6527,12 +7569,11 @@
       <c r="C253" s="6">
         <v>133.231547619048</v>
       </c>
-      <c r="D253" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E253" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D253,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D253" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E253" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F253" s="8">
         <v>585</v>
@@ -6549,7 +7590,7 @@
       <c r="C254" s="6">
         <v>133.76309523809499</v>
       </c>
-      <c r="D254" s="6">
+      <c r="D254" s="17">
         <v>2212</v>
       </c>
       <c r="E254" s="7" t="s">
@@ -6570,12 +7611,11 @@
       <c r="C255" s="6">
         <v>134.294642857143</v>
       </c>
-      <c r="D255" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E255" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D255,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D255" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E255" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F255" s="8">
         <v>4720</v>
@@ -6592,7 +7632,7 @@
       <c r="C256" s="6">
         <v>134.82619047618999</v>
       </c>
-      <c r="D256" s="6">
+      <c r="D256" s="17">
         <v>2212</v>
       </c>
       <c r="E256" s="7" t="s">
@@ -6613,12 +7653,11 @@
       <c r="C257" s="6">
         <v>135.35773809523801</v>
       </c>
-      <c r="D257" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E257" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D257,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D257" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E257" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F257" s="8">
         <v>7033</v>
@@ -6635,7 +7674,7 @@
       <c r="C258" s="6">
         <v>135.88928571428599</v>
       </c>
-      <c r="D258" s="6">
+      <c r="D258" s="17">
         <v>2212</v>
       </c>
       <c r="E258" s="7" t="s">
@@ -6656,12 +7695,11 @@
       <c r="C259" s="6">
         <v>136.42083333333301</v>
       </c>
-      <c r="D259" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E259" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D259,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D259" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E259" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F259" s="8">
         <v>1990</v>
@@ -6678,7 +7716,7 @@
       <c r="C260" s="6">
         <v>136.95238095238099</v>
       </c>
-      <c r="D260" s="6">
+      <c r="D260" s="17">
         <v>2212</v>
       </c>
       <c r="E260" s="7" t="s">
@@ -6699,12 +7737,11 @@
       <c r="C261" s="6">
         <v>137.483928571429</v>
       </c>
-      <c r="D261" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E261" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D261,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D261" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E261" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F261" s="8">
         <v>12673</v>
@@ -6721,7 +7758,7 @@
       <c r="C262" s="6">
         <v>138.01547619047599</v>
       </c>
-      <c r="D262" s="6">
+      <c r="D262" s="17">
         <v>2212</v>
       </c>
       <c r="E262" s="7" t="s">
@@ -6742,12 +7779,11 @@
       <c r="C263" s="6">
         <v>138.54702380952401</v>
       </c>
-      <c r="D263" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E263" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D263,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D263" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E263" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F263" s="8">
         <v>1170</v>
@@ -6764,7 +7800,7 @@
       <c r="C264" s="6">
         <v>139.078571428571</v>
       </c>
-      <c r="D264" s="6">
+      <c r="D264" s="17">
         <v>2212</v>
       </c>
       <c r="E264" s="7" t="s">
@@ -6785,12 +7821,11 @@
       <c r="C265" s="6">
         <v>139.61011904761901</v>
       </c>
-      <c r="D265" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E265" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D265,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D265" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E265" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F265" s="8">
         <v>6680</v>
@@ -6807,7 +7842,7 @@
       <c r="C266" s="6">
         <v>140.14166666666699</v>
       </c>
-      <c r="D266" s="6">
+      <c r="D266" s="17">
         <v>2211</v>
       </c>
       <c r="E266" s="7" t="s">
@@ -6828,12 +7863,11 @@
       <c r="C267" s="6">
         <v>140.67321428571401</v>
       </c>
-      <c r="D267" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E267" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D267,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D267" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E267" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F267" s="8">
         <v>6630</v>
@@ -6850,7 +7884,7 @@
       <c r="C268" s="6">
         <v>141.20476190476199</v>
       </c>
-      <c r="D268" s="6">
+      <c r="D268" s="17">
         <v>2211</v>
       </c>
       <c r="E268" s="7" t="s">
@@ -6871,12 +7905,11 @@
       <c r="C269" s="6">
         <v>141.73630952380901</v>
       </c>
-      <c r="D269" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E269" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D269,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D269" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E269" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F269" s="8">
         <v>2200</v>
@@ -6893,7 +7926,7 @@
       <c r="C270" s="6">
         <v>142.267857142857</v>
       </c>
-      <c r="D270" s="6">
+      <c r="D270" s="17">
         <v>2211</v>
       </c>
       <c r="E270" s="7" t="s">
@@ -6914,12 +7947,11 @@
       <c r="C271" s="6">
         <v>142.79940476190501</v>
       </c>
-      <c r="D271" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E271" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D271,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D271" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E271" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F271" s="8">
         <v>5345</v>
@@ -6936,7 +7968,7 @@
       <c r="C272" s="6">
         <v>143.330952380952</v>
       </c>
-      <c r="D272" s="6">
+      <c r="D272" s="17">
         <v>2211</v>
       </c>
       <c r="E272" s="7" t="s">
@@ -6957,12 +7989,11 @@
       <c r="C273" s="6">
         <v>143.86250000000001</v>
       </c>
-      <c r="D273" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E273" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D273,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D273" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E273" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F273" s="8">
         <v>2960</v>
@@ -6979,7 +8010,7 @@
       <c r="C274" s="6">
         <v>144.394047619048</v>
       </c>
-      <c r="D274" s="6">
+      <c r="D274" s="17">
         <v>2211</v>
       </c>
       <c r="E274" s="7" t="s">
@@ -7000,12 +8031,11 @@
       <c r="C275" s="6">
         <v>144.92559523809501</v>
       </c>
-      <c r="D275" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E275" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D275,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D275" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E275" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F275" s="8">
         <v>1185</v>
@@ -7022,7 +8052,7 @@
       <c r="C276" s="6">
         <v>145.457142857143</v>
       </c>
-      <c r="D276" s="6">
+      <c r="D276" s="17">
         <v>2211</v>
       </c>
       <c r="E276" s="7" t="s">
@@ -7043,12 +8073,11 @@
       <c r="C277" s="6">
         <v>145.98869047618999</v>
       </c>
-      <c r="D277" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E277" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D277,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D277" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E277" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F277" s="8">
         <v>25720</v>
@@ -7065,7 +8094,7 @@
       <c r="C278" s="6">
         <v>146.520238095238</v>
       </c>
-      <c r="D278" s="6">
+      <c r="D278" s="17">
         <v>2211</v>
       </c>
       <c r="E278" s="7" t="s">
@@ -7086,12 +8115,11 @@
       <c r="C279" s="6">
         <v>147.05178571428601</v>
       </c>
-      <c r="D279" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E279" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D279,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D279" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E279" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F279" s="8">
         <v>14550</v>
@@ -7108,7 +8136,7 @@
       <c r="C280" s="6">
         <v>147.583333333333</v>
       </c>
-      <c r="D280" s="6">
+      <c r="D280" s="17">
         <v>2211</v>
       </c>
       <c r="E280" s="7" t="s">
@@ -7129,12 +8157,11 @@
       <c r="C281" s="6">
         <v>148.11488095238099</v>
       </c>
-      <c r="D281" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E281" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D281,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D281" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E281" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F281" s="8">
         <v>10890</v>
@@ -7151,7 +8178,7 @@
       <c r="C282" s="6">
         <v>148.646428571428</v>
       </c>
-      <c r="D282" s="6">
+      <c r="D282" s="17">
         <v>2211</v>
       </c>
       <c r="E282" s="7" t="s">
@@ -7172,12 +8199,11 @@
       <c r="C283" s="6">
         <v>149.17797619047599</v>
       </c>
-      <c r="D283" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E283" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D283,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D283" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E283" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F283" s="8">
         <v>19540</v>
@@ -7194,7 +8220,7 @@
       <c r="C284" s="6">
         <v>149.709523809524</v>
       </c>
-      <c r="D284" s="6">
+      <c r="D284" s="17">
         <v>2211</v>
       </c>
       <c r="E284" s="7" t="s">
@@ -7215,12 +8241,11 @@
       <c r="C285" s="6">
         <v>150.24107142857099</v>
       </c>
-      <c r="D285" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E285" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D285,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D285" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E285" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F285" s="8">
         <v>10550</v>
@@ -7237,7 +8262,7 @@
       <c r="C286" s="6">
         <v>150.772619047619</v>
       </c>
-      <c r="D286" s="6">
+      <c r="D286" s="17">
         <v>2211</v>
       </c>
       <c r="E286" s="7" t="s">
@@ -7258,7 +8283,7 @@
       <c r="C287" s="6">
         <v>151.30416666666699</v>
       </c>
-      <c r="D287" s="6">
+      <c r="D287" s="17">
         <v>2211</v>
       </c>
       <c r="E287" s="7" t="s">
@@ -7279,12 +8304,11 @@
       <c r="C288" s="6">
         <v>151.835714285714</v>
       </c>
-      <c r="D288" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E288" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D288,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D288" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E288" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F288" s="8"/>
       <c r="G288" s="8">
@@ -7301,12 +8325,11 @@
       <c r="C289" s="6">
         <v>152.36726190476199</v>
       </c>
-      <c r="D289" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E289" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D289,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D289" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E289" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F289" s="8">
         <v>4600</v>
@@ -7323,7 +8346,7 @@
       <c r="C290" s="6">
         <v>152.89880952380901</v>
       </c>
-      <c r="D290" s="6">
+      <c r="D290" s="17">
         <v>2211</v>
       </c>
       <c r="E290" s="7" t="s">
@@ -7344,12 +8367,11 @@
       <c r="C291" s="6">
         <v>153.43035714285699</v>
       </c>
-      <c r="D291" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E291" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D291,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D291" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E291" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F291" s="8">
         <v>860</v>
@@ -7366,7 +8388,7 @@
       <c r="C292" s="6">
         <v>153.961904761905</v>
       </c>
-      <c r="D292" s="6">
+      <c r="D292" s="17">
         <v>2211</v>
       </c>
       <c r="E292" s="7" t="s">
@@ -7387,12 +8409,11 @@
       <c r="C293" s="6">
         <v>154.49345238095199</v>
       </c>
-      <c r="D293" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E293" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D293,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D293" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E293" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F293" s="8">
         <v>7150</v>
@@ -7409,7 +8430,7 @@
       <c r="C294" s="6">
         <v>155.02500000000001</v>
       </c>
-      <c r="D294" s="6">
+      <c r="D294" s="17">
         <v>2211</v>
       </c>
       <c r="E294" s="7" t="s">
@@ -7430,12 +8451,11 @@
       <c r="C295" s="6">
         <v>155.55654761904799</v>
       </c>
-      <c r="D295" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E295" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D295,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D295" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E295" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F295" s="8">
         <v>5820</v>
@@ -7452,7 +8472,7 @@
       <c r="C296" s="6">
         <v>156.08809523809501</v>
       </c>
-      <c r="D296" s="6">
+      <c r="D296" s="17">
         <v>2211</v>
       </c>
       <c r="E296" s="7" t="s">
@@ -7473,12 +8493,11 @@
       <c r="C297" s="6">
         <v>156.61964285714299</v>
       </c>
-      <c r="D297" s="6">
-        <v>5101</v>
-      </c>
-      <c r="E297" s="7" t="str">
-        <f>IFERROR(VLOOKUP(D297,'[1]دليل الحسابات'!$A$5:$E$102,2,0),"")</f>
-        <v>المشتريات</v>
+      <c r="D297" s="17">
+        <v>1391</v>
+      </c>
+      <c r="E297" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F297" s="8">
         <v>2400</v>
@@ -7495,7 +8514,7 @@
       <c r="C298" s="6">
         <v>157.15119047619001</v>
       </c>
-      <c r="D298" s="6">
+      <c r="D298" s="17">
         <v>2211</v>
       </c>
       <c r="E298" s="7" t="s">
@@ -7516,7 +8535,7 @@
       <c r="C299" s="6">
         <v>157.68273809523799</v>
       </c>
-      <c r="D299" s="6">
+      <c r="D299" s="17">
         <v>1211</v>
       </c>
       <c r="E299" s="7" t="s">
@@ -7537,10 +8556,10 @@
       <c r="C300" s="6">
         <v>158.21428571428601</v>
       </c>
-      <c r="D300" s="6">
+      <c r="D300" s="17">
         <v>4001</v>
       </c>
-      <c r="E300" s="11" t="s">
+      <c r="E300" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F300" s="8"/>
@@ -7558,7 +8577,7 @@
       <c r="C301" s="6">
         <v>158.745833333333</v>
       </c>
-      <c r="D301" s="6">
+      <c r="D301" s="17">
         <v>1211</v>
       </c>
       <c r="E301" s="7" t="s">
@@ -7579,10 +8598,10 @@
       <c r="C302" s="6">
         <v>159.27738095238101</v>
       </c>
-      <c r="D302" s="6">
+      <c r="D302" s="17">
         <v>4001</v>
       </c>
-      <c r="E302" s="11" t="s">
+      <c r="E302" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F302" s="8"/>
@@ -7593,24 +8612,31 @@
         <v>94</v>
       </c>
     </row>
+    <row r="303" spans="2:8">
+      <c r="F303" s="13">
+        <f>SUM(F3:F302)</f>
+        <v>861376</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:H302" xr:uid="{9A10BBC1-C1E5-406F-ACCB-ABF92E7F8642}"/>
-  <conditionalFormatting sqref="E69 E71 E77 E95 E105 E145 E165 E168:E169 E185 E191 E204 E211 E217 E243 E232 E301 E234 E97 E107 E125 E142:E143 E153 E161 E171 E183 E213 E127 E189 E209 E249:E299">
-    <cfRule type="expression" dxfId="4" priority="46">
+  <autoFilter ref="B2:H303" xr:uid="{9A10BBC1-C1E5-406F-ACCB-ABF92E7F8642}"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="D142 D204 D232 D299 D301">
+    <cfRule type="expression" dxfId="4" priority="54">
+      <formula>#REF!="غير نشط"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E69 E95 E97 E107 E125 E127 E142:E143 E153 E161 E168 E171 E183 E189 E191 E204 E209 E213 E232 E234 E250 E252 E254 E256 E258 E260 E262 E264 E266 E268 E270 E272 E274 E276 E278 E280 E282 E284 E286:E287 E290 E292 E294 E296 E298:E299 E301">
+    <cfRule type="expression" dxfId="3" priority="46">
       <formula>AND($C69&lt;&gt;"",$D69="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G302">
-    <cfRule type="expression" dxfId="3" priority="51">
+    <cfRule type="expression" dxfId="2" priority="51">
       <formula>AND(#REF!&gt;0,$F3&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D142 D204 D232 D299 D301">
-    <cfRule type="expression" dxfId="2" priority="54">
-      <formula>#REF!="غير نشط"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E142 F233:H233 D243:E243 D211:E211 D191:E191 D185:E185 D168:E169 D165:E165 D155 D145:E145 D105:E105 D95:E95 D77:E77 D71:E71 D69:E69 F235:H298 D217:E217 E204 B3:C302 D300 F300:H300 D302 F302:H302 F3:H231 E232:H232 E299:H299 E301:H301 D234:H234 D97:E97 D107:E107 D125:E125 D143:E143 D153:E153 D161:E161 D171:E171 D183:E183 D213:E213 D127:E127 D189:E189 D209:E209 D249:E298">
+  <conditionalFormatting sqref="F3:H231 B3:C302 D69:E69 D71 D77 D95:E95 D97:E97 D105 D107:E107 D125:E125 D127:E127 E142 D143:E143 D145 D153:E153 D155 D161:E161 D165 D168:E168 D169 D171:E171 D183:E183 D185 D189:E189 D191:E191 E204 D209:E209 D211 D213:E213 D217 E232:H232 F233:H233 D234:H234 F235:H298 D243 D249 D250:E250 D251 D252:E252 D253 D254:E254 D255 D256:E256 D257 D258:E258 D259 D260:E260 D261 D262:E262 D263 D264:E264 D265 D266:E266 D267 D268:E268 D269 D270:E270 D271 D272:E272 D273 D274:E274 D275 D276:E276 D277 D278:E278 D279 D280:E280 D281 D282:E282 D283 D284:E284 D285 D286:E287 D288:D289 D290:E290 D291 D292:E292 D293 D294:E294 D295 D296:E296 D297 D298:E298 E299:H299 D300 F300:H300 E301:H301 D302 F302:H302">
     <cfRule type="expression" dxfId="1" priority="59">
       <formula>#REF!="غير متوازن"</formula>
     </cfRule>
@@ -7627,10 +8653,10 @@
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D97 D213 D232 D211 D243 D183 D168:D169 D165 D234 D161 D189 D77 D204 D95 D105 D69 D127 D107 D209 D153 D71 D155 D145 D191 D171 D185 D125 D143 D217 D249:D302" xr:uid="{D01A0CB3-D779-4795-994A-5F8BA9E0214E}">
+    <dataValidation type="list" allowBlank="1" sqref="D97 D213 D232 D185 D243 D183 D165 D145 D234 D161 D189 D217 D204 D95 D105 D69 D127 D107 D209 D153 D71 D155 D77 D191 D171 D168:D169 D125 D143 D211 D249:D302" xr:uid="{D01A0CB3-D779-4795-994A-5F8BA9E0214E}">
       <formula1>AccountCodes</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="قيمة غير مسموح بها" error="يرجى الاختيار من القائمة المحددة فقط." promptTitle="قائمة اختيار" prompt="اختر كود الحساب من دليل الحسابات." sqref="D209 D107 D145 D234 D155 D243 D183 D161 D95 D185 D125 D143 D69 D168:D169 D189 D165 D217 D153 D77 D127 D171 D302 D105 D211 D97 D191 D71 D213 D300 D249:D298" xr:uid="{DDDA10A1-3C52-47FA-AF5A-9CC30A6B5B2E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="قيمة غير مسموح بها" error="يرجى الاختيار من القائمة المحددة فقط." promptTitle="قائمة اختيار" prompt="اختر كود الحساب من دليل الحسابات." sqref="D209 D107 D77 D234 D155 D243 D183 D161 D95 D168:D169 D125 D143 D69 D165 D189 D145 D211 D153 D217 D127 D171 D302 D105 D185 D97 D191 D71 D213 D300 D249:D298" xr:uid="{DDDA10A1-3C52-47FA-AF5A-9CC30A6B5B2E}">
       <formula1>AccountCodes</formula1>
       <formula2>0</formula2>
     </dataValidation>
